--- a/Conciliacao_Pe_de_Manga_2026-07.xlsx
+++ b/Conciliacao_Pe_de_Manga_2026-07.xlsx
@@ -14,6 +14,7 @@
     <sheet name="D_Duplicidades_Excel" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="E_Fatura_falta_Everest" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="F_Fatura_completa" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="G_Fatura_falta_Excel" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,8 +24,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -114,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -135,18 +136,23 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -512,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1009,6 +1015,88 @@
         <is>
           <t>- Fatura Agosto: pagamento fatura anterior -38.526 + estornos anuidade + 16 estornos (R$ 4.346 refunds).</t>
         </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3">
+        <f>== RECON C: Fatura Agosto x Excel Julho ===</f>
+        <v/>
+      </c>
+      <c r="C56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Casam por valor</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="n"/>
+      <c r="C57" s="5" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>Fatura SEM Excel qtde</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="n"/>
+      <c r="C58" s="7" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>Fatura SEM Excel valor R$</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n"/>
+      <c r="C59" s="9" t="n">
+        <v>26115.98</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Mercadoria - DEVE LANCAR NO EXCEL qtde</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="n"/>
+      <c r="C60" s="10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Mercadoria - valor R$</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="n"/>
+      <c r="C61" s="12" t="n">
+        <v>2625.65</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Servico/app qtde</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Servico/app valor R$</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>23490.33</v>
       </c>
     </row>
   </sheetData>
@@ -1088,13 +1176,13 @@
       <c r="D2" s="17" t="n">
         <v>805494</v>
       </c>
-      <c r="E2" s="18" t="n">
+      <c r="E2" s="30" t="n">
         <v>46203.51736111111</v>
       </c>
       <c r="F2" s="19" t="n">
         <v>6860.5</v>
       </c>
-      <c r="G2" s="18" t="n">
+      <c r="G2" s="30" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1115,13 +1203,13 @@
       <c r="D3" s="17" t="n">
         <v>5018</v>
       </c>
-      <c r="E3" s="18" t="n">
+      <c r="E3" s="30" t="n">
         <v>46210.47777777778</v>
       </c>
       <c r="F3" s="19" t="n">
         <v>4293.24</v>
       </c>
-      <c r="G3" s="18" t="n">
+      <c r="G3" s="30" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -1142,13 +1230,13 @@
       <c r="D4" s="17" t="n">
         <v>54532</v>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="30" t="n">
         <v>46180.49657407407</v>
       </c>
       <c r="F4" s="19" t="n">
         <v>1811.4</v>
       </c>
-      <c r="G4" s="18" t="n">
+      <c r="G4" s="30" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -1169,13 +1257,13 @@
       <c r="D5" s="17" t="n">
         <v>475</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="30" t="n">
         <v>46181.36820601852</v>
       </c>
       <c r="F5" s="19" t="n">
         <v>1660</v>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="G5" s="30" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -1196,13 +1284,13 @@
       <c r="D6" s="17" t="n">
         <v>247057</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="30" t="n">
         <v>46203.93840277778</v>
       </c>
       <c r="F6" s="19" t="n">
         <v>1630.58</v>
       </c>
-      <c r="G6" s="18" t="n">
+      <c r="G6" s="30" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1223,13 +1311,13 @@
       <c r="D7" s="17" t="n">
         <v>26286</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="30" t="n">
         <v>46224.42430555556</v>
       </c>
       <c r="F7" s="19" t="n">
         <v>1217.37</v>
       </c>
-      <c r="G7" s="18" t="n">
+      <c r="G7" s="30" t="n">
         <v>46225</v>
       </c>
     </row>
@@ -1250,13 +1338,13 @@
       <c r="D8" s="17" t="n">
         <v>733649</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="30" t="n">
         <v>46230.51597222222</v>
       </c>
       <c r="F8" s="19" t="n">
         <v>1114.19</v>
       </c>
-      <c r="G8" s="18" t="n">
+      <c r="G8" s="30" t="n">
         <v>46231</v>
       </c>
     </row>
@@ -1277,13 +1365,13 @@
       <c r="D9" s="14" t="n">
         <v>20330</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="31" t="n">
         <v>46224.70079861111</v>
       </c>
       <c r="F9" s="15" t="n">
         <v>875</v>
       </c>
-      <c r="G9" s="20" t="n">
+      <c r="G9" s="31" t="n">
         <v>46224</v>
       </c>
     </row>
@@ -1304,13 +1392,13 @@
       <c r="D10" s="14" t="n">
         <v>2055173</v>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="31" t="n">
         <v>46224.22569444445</v>
       </c>
       <c r="F10" s="15" t="n">
         <v>506.82</v>
       </c>
-      <c r="G10" s="20" t="n">
+      <c r="G10" s="31" t="n">
         <v>46224</v>
       </c>
     </row>
@@ -1331,13 +1419,13 @@
       <c r="D11" s="14" t="n">
         <v>20258</v>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="31" t="n">
         <v>46213.45891203704</v>
       </c>
       <c r="F11" s="15" t="n">
         <v>500</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="31" t="n">
         <v>46213</v>
       </c>
     </row>
@@ -1358,13 +1446,13 @@
       <c r="D12" s="14" t="n">
         <v>6222</v>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="31" t="n">
         <v>46182.6609375</v>
       </c>
       <c r="F12" s="15" t="n">
         <v>397.32</v>
       </c>
-      <c r="G12" s="20" t="n">
+      <c r="G12" s="31" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -1385,13 +1473,13 @@
       <c r="D13" s="14" t="n">
         <v>46843</v>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="31" t="n">
         <v>46223.65697916667</v>
       </c>
       <c r="F13" s="15" t="n">
         <v>392.35</v>
       </c>
-      <c r="G13" s="20" t="n">
+      <c r="G13" s="31" t="n">
         <v>46224</v>
       </c>
     </row>
@@ -1412,13 +1500,13 @@
       <c r="D14" s="14" t="n">
         <v>738090</v>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="31" t="n">
         <v>46206.46072916667</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>298.22</v>
       </c>
-      <c r="G14" s="20" t="n">
+      <c r="G14" s="31" t="n">
         <v>46206</v>
       </c>
     </row>
@@ -1439,13 +1527,13 @@
       <c r="D15" s="14" t="n">
         <v>6224</v>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" s="31" t="n">
         <v>46182.66099537037</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>264.88</v>
       </c>
-      <c r="G15" s="20" t="n">
+      <c r="G15" s="31" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -1466,13 +1554,13 @@
       <c r="D16" s="14" t="n">
         <v>58696</v>
       </c>
-      <c r="E16" s="20" t="n">
+      <c r="E16" s="31" t="n">
         <v>46203.78267361111</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>245.4</v>
       </c>
-      <c r="G16" s="20" t="n">
+      <c r="G16" s="31" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1493,13 +1581,13 @@
       <c r="D17" s="14" t="n">
         <v>483574</v>
       </c>
-      <c r="E17" s="20" t="n">
+      <c r="E17" s="31" t="n">
         <v>46223.91938657407</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>212.26</v>
       </c>
-      <c r="G17" s="20" t="n">
+      <c r="G17" s="31" t="n">
         <v>46224</v>
       </c>
     </row>
@@ -1520,13 +1608,13 @@
       <c r="D18" s="14" t="n">
         <v>128737927</v>
       </c>
-      <c r="E18" s="20" t="n">
+      <c r="E18" s="31" t="n">
         <v>46183.97166666666</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>159</v>
       </c>
-      <c r="G18" s="20" t="n">
+      <c r="G18" s="31" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -1547,13 +1635,13 @@
       <c r="D19" s="14" t="n">
         <v>128737935</v>
       </c>
-      <c r="E19" s="20" t="n">
+      <c r="E19" s="31" t="n">
         <v>46183.97168981482</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>159</v>
       </c>
-      <c r="G19" s="20" t="n">
+      <c r="G19" s="31" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -1574,13 +1662,13 @@
       <c r="D20" s="14" t="n">
         <v>10973</v>
       </c>
-      <c r="E20" s="20" t="n">
+      <c r="E20" s="31" t="n">
         <v>46191.33802083333</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>147.95</v>
       </c>
-      <c r="G20" s="20" t="n">
+      <c r="G20" s="31" t="n">
         <v>46221</v>
       </c>
     </row>
@@ -1601,13 +1689,13 @@
       <c r="D21" s="14" t="n">
         <v>767768</v>
       </c>
-      <c r="E21" s="20" t="n">
+      <c r="E21" s="31" t="n">
         <v>46182.51445601852</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>146</v>
       </c>
-      <c r="G21" s="20" t="n">
+      <c r="G21" s="31" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -1628,13 +1716,13 @@
       <c r="D22" s="14" t="n">
         <v>805420</v>
       </c>
-      <c r="E22" s="20" t="n">
+      <c r="E22" s="31" t="n">
         <v>46203.39236111111</v>
       </c>
       <c r="F22" s="15" t="n">
         <v>78.16</v>
       </c>
-      <c r="G22" s="20" t="n">
+      <c r="G22" s="31" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1655,13 +1743,13 @@
       <c r="D23" s="14" t="n">
         <v>267309</v>
       </c>
-      <c r="E23" s="20" t="n">
+      <c r="E23" s="31" t="n">
         <v>46216.91094907407</v>
       </c>
       <c r="F23" s="15" t="n">
         <v>76.17</v>
       </c>
-      <c r="G23" s="20" t="n">
+      <c r="G23" s="31" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -1682,13 +1770,13 @@
       <c r="D24" s="14" t="n">
         <v>247058</v>
       </c>
-      <c r="E24" s="20" t="n">
+      <c r="E24" s="31" t="n">
         <v>46203.93840277778</v>
       </c>
       <c r="F24" s="15" t="n">
         <v>72.23</v>
       </c>
-      <c r="G24" s="20" t="n">
+      <c r="G24" s="31" t="n">
         <v>46204</v>
       </c>
     </row>
@@ -1709,13 +1797,13 @@
       <c r="D25" s="14" t="n">
         <v>257033</v>
       </c>
-      <c r="E25" s="20" t="n">
+      <c r="E25" s="31" t="n">
         <v>46209.88335648148</v>
       </c>
       <c r="F25" s="15" t="n">
         <v>68.98999999999999</v>
       </c>
-      <c r="G25" s="20" t="n">
+      <c r="G25" s="31" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -1736,13 +1824,13 @@
       <c r="D26" s="14" t="n">
         <v>47670</v>
       </c>
-      <c r="E26" s="20" t="n">
+      <c r="E26" s="31" t="n">
         <v>46178.46302083333</v>
       </c>
       <c r="F26" s="15" t="n">
         <v>68.44</v>
       </c>
-      <c r="G26" s="20" t="n">
+      <c r="G26" s="31" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -1763,13 +1851,13 @@
       <c r="D27" s="14" t="n">
         <v>138526799</v>
       </c>
-      <c r="E27" s="20" t="n">
+      <c r="E27" s="31" t="n">
         <v>46219.63215277778</v>
       </c>
       <c r="F27" s="15" t="n">
         <v>59.9</v>
       </c>
-      <c r="G27" s="20" t="n">
+      <c r="G27" s="31" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -1790,13 +1878,13 @@
       <c r="D28" s="14" t="n">
         <v>138526960</v>
       </c>
-      <c r="E28" s="20" t="n">
+      <c r="E28" s="31" t="n">
         <v>46219.63291666667</v>
       </c>
       <c r="F28" s="15" t="n">
         <v>59.9</v>
       </c>
-      <c r="G28" s="20" t="n">
+      <c r="G28" s="31" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -1817,13 +1905,13 @@
       <c r="D29" s="14" t="n">
         <v>138527147</v>
       </c>
-      <c r="E29" s="20" t="n">
+      <c r="E29" s="31" t="n">
         <v>46219.63386574074</v>
       </c>
       <c r="F29" s="15" t="n">
         <v>59.9</v>
       </c>
-      <c r="G29" s="20" t="n">
+      <c r="G29" s="31" t="n">
         <v>46219</v>
       </c>
     </row>
@@ -1844,13 +1932,13 @@
       <c r="D30" s="14" t="n">
         <v>257032</v>
       </c>
-      <c r="E30" s="20" t="n">
+      <c r="E30" s="31" t="n">
         <v>46209.88335648148</v>
       </c>
       <c r="F30" s="15" t="n">
         <v>39</v>
       </c>
-      <c r="G30" s="20" t="n">
+      <c r="G30" s="31" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -1871,13 +1959,13 @@
       <c r="D31" s="14" t="n">
         <v>257034</v>
       </c>
-      <c r="E31" s="20" t="n">
+      <c r="E31" s="31" t="n">
         <v>46209.88335648148</v>
       </c>
       <c r="F31" s="15" t="n">
         <v>30.1</v>
       </c>
-      <c r="G31" s="20" t="n">
+      <c r="G31" s="31" t="n">
         <v>46211</v>
       </c>
     </row>
@@ -1898,13 +1986,13 @@
       <c r="D32" s="14" t="n">
         <v>267308</v>
       </c>
-      <c r="E32" s="20" t="n">
+      <c r="E32" s="31" t="n">
         <v>46216.91094907407</v>
       </c>
       <c r="F32" s="15" t="n">
         <v>18.06</v>
       </c>
-      <c r="G32" s="20" t="n">
+      <c r="G32" s="31" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -1923,13 +2011,13 @@
         <v>15380</v>
       </c>
       <c r="D33" s="14" t="n"/>
-      <c r="E33" s="20" t="n">
+      <c r="E33" s="31" t="n">
         <v>46230.42800925926</v>
       </c>
       <c r="F33" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="G33" s="20" t="n">
+      <c r="G33" s="31" t="n">
         <v>46230</v>
       </c>
     </row>
@@ -1950,13 +2038,13 @@
       <c r="D34" s="14" t="n">
         <v>267307</v>
       </c>
-      <c r="E34" s="20" t="n">
+      <c r="E34" s="31" t="n">
         <v>46216.91094907407</v>
       </c>
       <c r="F34" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="G34" s="20" t="n">
+      <c r="G34" s="31" t="n">
         <v>46217</v>
       </c>
     </row>
@@ -2014,7 +2102,7 @@
           <t xml:space="preserve">ST ETIENNE CITY PADARIA E CONFEITARIA LTDA  - FIXO </t>
         </is>
       </c>
-      <c r="B2" s="22" t="n">
+      <c r="B2" s="32" t="n">
         <v>46233</v>
       </c>
       <c r="C2" s="23" t="n">
@@ -2037,7 +2125,7 @@
           <t>KHADUN B. LIMA</t>
         </is>
       </c>
-      <c r="B3" s="22" t="n">
+      <c r="B3" s="32" t="n">
         <v>46218</v>
       </c>
       <c r="C3" s="23" t="n">
@@ -2060,7 +2148,7 @@
           <t>SCHIPPER CONS</t>
         </is>
       </c>
-      <c r="B4" s="22" t="n">
+      <c r="B4" s="32" t="n">
         <v>46234</v>
       </c>
       <c r="C4" s="23" t="n">
@@ -2083,7 +2171,7 @@
           <t>REAL COMERCIAL LTDA</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n">
+      <c r="B5" s="32" t="n">
         <v>46230</v>
       </c>
       <c r="C5" s="23" t="n">
@@ -2106,7 +2194,7 @@
           <t>NOMADE BAR E RESTAURANTE LTDA</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="32" t="n">
         <v>46224</v>
       </c>
       <c r="C6" s="23" t="n">
@@ -2129,7 +2217,7 @@
           <t>FRAN ADESIVOS</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="32" t="n">
         <v>46224</v>
       </c>
       <c r="C7" s="23" t="n">
@@ -2152,7 +2240,7 @@
           <t>MULTIFOODS COM DE ALIM E BEBIDAS LTDA</t>
         </is>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="32" t="n">
         <v>46224</v>
       </c>
       <c r="C8" s="23" t="n">
@@ -2175,7 +2263,7 @@
           <t>NOMADE BAR E RESTAURANTE LTDA</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="32" t="n">
         <v>46218</v>
       </c>
       <c r="C9" s="23" t="n">
@@ -2198,7 +2286,7 @@
           <t>QUALIVE IMP E COMERCIO DE ALIMENTOS LTDA</t>
         </is>
       </c>
-      <c r="B10" s="22" t="n">
+      <c r="B10" s="32" t="n">
         <v>46214</v>
       </c>
       <c r="C10" s="23" t="n">
@@ -2221,7 +2309,7 @@
           <t>MARIO PEDRO FELICIANO HORTIFRUTI EPP</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n">
+      <c r="B11" s="32" t="n">
         <v>46223</v>
       </c>
       <c r="C11" s="23" t="n">
@@ -2244,7 +2332,7 @@
           <t>FESTA E CIA</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n">
+      <c r="B12" s="32" t="n">
         <v>46207</v>
       </c>
       <c r="C12" s="23" t="n">
@@ -2267,7 +2355,7 @@
           <t>BANCA DO RAMOM</t>
         </is>
       </c>
-      <c r="B13" s="22" t="n">
+      <c r="B13" s="32" t="n">
         <v>46206</v>
       </c>
       <c r="C13" s="23" t="n">
@@ -2290,7 +2378,7 @@
           <t>SHEILA MARIA NUNES</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n">
+      <c r="B14" s="32" t="n">
         <v>46224</v>
       </c>
       <c r="C14" s="23" t="n">
@@ -2313,7 +2401,7 @@
           <t>CHAME ATAC.</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n">
+      <c r="B15" s="32" t="n">
         <v>46219</v>
       </c>
       <c r="C15" s="23" t="n">
@@ -2336,7 +2424,7 @@
           <t xml:space="preserve">HORTIFRUTI POMAR DA VILA E MERCEARIA LTDA </t>
         </is>
       </c>
-      <c r="B16" s="22" t="n">
+      <c r="B16" s="32" t="n">
         <v>46227</v>
       </c>
       <c r="C16" s="23" t="n">
@@ -2359,7 +2447,7 @@
           <t xml:space="preserve">HORTIFRUTI POMAR DA VILA E MERCEARIA LTDA </t>
         </is>
       </c>
-      <c r="B17" s="22" t="n">
+      <c r="B17" s="32" t="n">
         <v>46224</v>
       </c>
       <c r="C17" s="23" t="n">
@@ -2382,7 +2470,7 @@
           <t xml:space="preserve">HORTIFRUTI POMAR DA VILA E MERCEARIA LTDA </t>
         </is>
       </c>
-      <c r="B18" s="22" t="n">
+      <c r="B18" s="32" t="n">
         <v>46228</v>
       </c>
       <c r="C18" s="23" t="n">
@@ -2405,7 +2493,7 @@
           <t xml:space="preserve">HORTIFRUTI POMAR DA VILA E MERCEARIA LTDA </t>
         </is>
       </c>
-      <c r="B19" s="22" t="n">
+      <c r="B19" s="32" t="n">
         <v>46205</v>
       </c>
       <c r="C19" s="23" t="n">
@@ -2428,7 +2516,7 @@
           <t>TL DISTRIBUIDORA</t>
         </is>
       </c>
-      <c r="B20" s="22" t="n">
+      <c r="B20" s="32" t="n">
         <v>46219</v>
       </c>
       <c r="C20" s="23" t="n">
@@ -2451,7 +2539,7 @@
           <t>GOOGLE</t>
         </is>
       </c>
-      <c r="B21" s="20" t="n">
+      <c r="B21" s="31" t="n">
         <v>46234</v>
       </c>
       <c r="C21" s="15" t="n">
@@ -2474,7 +2562,7 @@
           <t>META</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n">
+      <c r="B22" s="31" t="n">
         <v>46234</v>
       </c>
       <c r="C22" s="15" t="n">
@@ -2497,7 +2585,7 @@
           <t>AGENCIA LINKADAS</t>
         </is>
       </c>
-      <c r="B23" s="20" t="n">
+      <c r="B23" s="31" t="n">
         <v>46203</v>
       </c>
       <c r="C23" s="15" t="n">
@@ -2520,7 +2608,7 @@
           <t>FABIO ROSOCHASNKY - DELLAS CONECTING</t>
         </is>
       </c>
-      <c r="B24" s="20" t="n">
+      <c r="B24" s="31" t="n">
         <v>46203</v>
       </c>
       <c r="C24" s="15" t="n">
@@ -2543,7 +2631,7 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n">
+      <c r="B25" s="31" t="n">
         <v>46203</v>
       </c>
       <c r="C25" s="15" t="n">
@@ -2566,7 +2654,7 @@
           <t>MMACR PRODUCOES LTDA -  MARCELA MALUF -EFFE HUB</t>
         </is>
       </c>
-      <c r="B26" s="20" t="n">
+      <c r="B26" s="31" t="n">
         <v>46203</v>
       </c>
       <c r="C26" s="15" t="n">
@@ -2589,7 +2677,7 @@
           <t>ANTHROPIC, PBC</t>
         </is>
       </c>
-      <c r="B27" s="20" t="n">
+      <c r="B27" s="31" t="n">
         <v>46222</v>
       </c>
       <c r="C27" s="15" t="n">
@@ -2612,7 +2700,7 @@
           <t>CAMILA VIEIRA - MY TEAM</t>
         </is>
       </c>
-      <c r="B28" s="20" t="n">
+      <c r="B28" s="31" t="n">
         <v>46203</v>
       </c>
       <c r="C28" s="15" t="n">
@@ -2635,7 +2723,7 @@
           <t>COMERCIO E INDUSTRIA DE VELAS AIB EIRELI ME</t>
         </is>
       </c>
-      <c r="B29" s="20" t="n">
+      <c r="B29" s="31" t="n">
         <v>46210</v>
       </c>
       <c r="C29" s="15" t="n">
@@ -2658,7 +2746,7 @@
           <t>TRIPADVISOR</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n">
+      <c r="B30" s="31" t="n">
         <v>46207</v>
       </c>
       <c r="C30" s="15" t="n">
@@ -2681,7 +2769,7 @@
           <t>JESUS DECOR DISTRIBUIDORA LTDA</t>
         </is>
       </c>
-      <c r="B31" s="20" t="n">
+      <c r="B31" s="31" t="n">
         <v>46216</v>
       </c>
       <c r="C31" s="15" t="n">
@@ -2704,7 +2792,7 @@
           <t>RYZE AL</t>
         </is>
       </c>
-      <c r="B32" s="20" t="n">
+      <c r="B32" s="31" t="n">
         <v>46204</v>
       </c>
       <c r="C32" s="15" t="n">
@@ -2727,7 +2815,7 @@
           <t>HIGGSFILED INC.</t>
         </is>
       </c>
-      <c r="B33" s="20" t="n">
+      <c r="B33" s="31" t="n">
         <v>46229</v>
       </c>
       <c r="C33" s="15" t="n">
@@ -2750,7 +2838,7 @@
           <t>AUTO POSTO MORUMBI</t>
         </is>
       </c>
-      <c r="B34" s="20" t="n">
+      <c r="B34" s="31" t="n">
         <v>46218</v>
       </c>
       <c r="C34" s="15" t="n">
@@ -2773,7 +2861,7 @@
           <t>PC GAMER INFORMATICA</t>
         </is>
       </c>
-      <c r="B35" s="20" t="n">
+      <c r="B35" s="31" t="n">
         <v>46209</v>
       </c>
       <c r="C35" s="15" t="n">
@@ -2796,7 +2884,7 @@
           <t>ALIEXPRESS</t>
         </is>
       </c>
-      <c r="B36" s="20" t="n">
+      <c r="B36" s="31" t="n">
         <v>46204</v>
       </c>
       <c r="C36" s="15" t="n">
@@ -2819,7 +2907,7 @@
           <t>LALAMOVE</t>
         </is>
       </c>
-      <c r="B37" s="20" t="n">
+      <c r="B37" s="31" t="n">
         <v>46234</v>
       </c>
       <c r="C37" s="15" t="n">
@@ -2842,7 +2930,7 @@
           <t>TRADAQ LTDA</t>
         </is>
       </c>
-      <c r="B38" s="20" t="n">
+      <c r="B38" s="31" t="n">
         <v>46233</v>
       </c>
       <c r="C38" s="15" t="n">
@@ -2865,7 +2953,7 @@
           <t>OPENAI *CHATGPT SUBSCR</t>
         </is>
       </c>
-      <c r="B39" s="20" t="n">
+      <c r="B39" s="31" t="n">
         <v>46232</v>
       </c>
       <c r="C39" s="15" t="n">
@@ -2888,7 +2976,7 @@
           <t>DEPOSITO LA TERZA</t>
         </is>
       </c>
-      <c r="B40" s="20" t="n">
+      <c r="B40" s="31" t="n">
         <v>46225</v>
       </c>
       <c r="C40" s="15" t="n">
@@ -2911,7 +2999,7 @@
           <t xml:space="preserve">PERMUTE - PRESTADORA DE SERVIÇOS </t>
         </is>
       </c>
-      <c r="B41" s="20" t="n">
+      <c r="B41" s="31" t="n">
         <v>46233</v>
       </c>
       <c r="C41" s="15" t="n">
@@ -2934,7 +3022,7 @@
           <t>LILI MEDICINA E SEGURANÇA DE TRABALHO LTDA</t>
         </is>
       </c>
-      <c r="B42" s="20" t="n">
+      <c r="B42" s="31" t="n">
         <v>46233</v>
       </c>
       <c r="C42" s="15" t="n">
@@ -2957,7 +3045,7 @@
           <t>MERCADO LIVRE</t>
         </is>
       </c>
-      <c r="B43" s="20" t="n">
+      <c r="B43" s="31" t="n">
         <v>46225</v>
       </c>
       <c r="C43" s="15" t="n">
@@ -2980,7 +3068,7 @@
           <t>MERCADO LIVRE</t>
         </is>
       </c>
-      <c r="B44" s="20" t="n">
+      <c r="B44" s="31" t="n">
         <v>46219</v>
       </c>
       <c r="C44" s="15" t="n">
@@ -3003,7 +3091,7 @@
           <t xml:space="preserve">UBER </t>
         </is>
       </c>
-      <c r="B45" s="20" t="n">
+      <c r="B45" s="31" t="n">
         <v>46204</v>
       </c>
       <c r="C45" s="15" t="n">
@@ -3099,7 +3187,7 @@
           <t>CDL SAO PAULO</t>
         </is>
       </c>
-      <c r="B4" s="25" t="n">
+      <c r="B4" s="33" t="n">
         <v>46203.93840277778</v>
       </c>
       <c r="C4" s="26" t="n">
@@ -3110,7 +3198,7 @@
           <t>FABIO ROSOCHASNKY - DELLAS CONECTING</t>
         </is>
       </c>
-      <c r="E4" s="25" t="n">
+      <c r="E4" s="33" t="n">
         <v>46203</v>
       </c>
       <c r="F4" s="26" t="n">
@@ -3129,7 +3217,7 @@
           <t>FREIXENET</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n">
+      <c r="B5" s="33" t="n">
         <v>46224.42430555556</v>
       </c>
       <c r="C5" s="26" t="n">
@@ -3140,7 +3228,7 @@
           <t>REAL COMERCIAL LTDA</t>
         </is>
       </c>
-      <c r="E5" s="25" t="n">
+      <c r="E5" s="33" t="n">
         <v>46230</v>
       </c>
       <c r="F5" s="26" t="n">
@@ -3159,7 +3247,7 @@
           <t>MULTFOODS</t>
         </is>
       </c>
-      <c r="B6" s="25" t="n">
+      <c r="B6" s="33" t="n">
         <v>46224.22569444445</v>
       </c>
       <c r="C6" s="26" t="n">
@@ -3170,7 +3258,7 @@
           <t>FRAN ADESIVOS</t>
         </is>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="33" t="n">
         <v>46224</v>
       </c>
       <c r="F6" s="26" t="n">
@@ -3189,7 +3277,7 @@
           <t>ULTRA CLASSIC</t>
         </is>
       </c>
-      <c r="B7" s="25" t="n">
+      <c r="B7" s="33" t="n">
         <v>46213.45891203704</v>
       </c>
       <c r="C7" s="26" t="n">
@@ -3200,7 +3288,7 @@
           <t>ANTHROPIC, PBC</t>
         </is>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="33" t="n">
         <v>46222</v>
       </c>
       <c r="F7" s="26" t="n">
@@ -3219,7 +3307,7 @@
           <t>AIB VELAS</t>
         </is>
       </c>
-      <c r="B8" s="25" t="n">
+      <c r="B8" s="33" t="n">
         <v>46223.65697916667</v>
       </c>
       <c r="C8" s="26" t="n">
@@ -3230,7 +3318,7 @@
           <t>NOMADE BAR E RESTAURANTE LTDA</t>
         </is>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="33" t="n">
         <v>46218</v>
       </c>
       <c r="F8" s="26" t="n">
@@ -3249,7 +3337,7 @@
           <t>KALUNGA SA</t>
         </is>
       </c>
-      <c r="B9" s="25" t="n">
+      <c r="B9" s="33" t="n">
         <v>46206.46072916667</v>
       </c>
       <c r="C9" s="26" t="n">
@@ -3260,7 +3348,7 @@
           <t>QUALIVE IMP E COMERCIO DE ALIMENTOS LTDA</t>
         </is>
       </c>
-      <c r="E9" s="25" t="n">
+      <c r="E9" s="33" t="n">
         <v>46214</v>
       </c>
       <c r="F9" s="26" t="n">
@@ -3279,7 +3367,7 @@
           <t>PIMENTA ROSA</t>
         </is>
       </c>
-      <c r="B10" s="25" t="n">
+      <c r="B10" s="33" t="n">
         <v>46203.78267361111</v>
       </c>
       <c r="C10" s="26" t="n">
@@ -3290,7 +3378,7 @@
           <t>PC GAMER INFORMATICA</t>
         </is>
       </c>
-      <c r="E10" s="25" t="n">
+      <c r="E10" s="33" t="n">
         <v>46209</v>
       </c>
       <c r="F10" s="26" t="n">
@@ -3309,7 +3397,7 @@
           <t>ELO - FRUTI</t>
         </is>
       </c>
-      <c r="B11" s="25" t="n">
+      <c r="B11" s="33" t="n">
         <v>46223.91938657407</v>
       </c>
       <c r="C11" s="26" t="n">
@@ -3320,7 +3408,7 @@
           <t>MARIO PEDRO FELICIANO HORTIFRUTI EPP</t>
         </is>
       </c>
-      <c r="E11" s="25" t="n">
+      <c r="E11" s="33" t="n">
         <v>46223</v>
       </c>
       <c r="F11" s="26" t="n">
@@ -3339,7 +3427,7 @@
           <t>MISTRAL</t>
         </is>
       </c>
-      <c r="B12" s="25" t="n">
+      <c r="B12" s="33" t="n">
         <v>46203.39236111111</v>
       </c>
       <c r="C12" s="26" t="n">
@@ -3350,7 +3438,7 @@
           <t>BANCA DO RAMOM</t>
         </is>
       </c>
-      <c r="E12" s="25" t="n">
+      <c r="E12" s="33" t="n">
         <v>46206</v>
       </c>
       <c r="F12" s="26" t="n">
@@ -3369,7 +3457,7 @@
           <t>CDL SAO PAULO</t>
         </is>
       </c>
-      <c r="B13" s="25" t="n">
+      <c r="B13" s="33" t="n">
         <v>46216.91094907407</v>
       </c>
       <c r="C13" s="26" t="n">
@@ -3380,7 +3468,7 @@
           <t>SHEILA MARIA NUNES</t>
         </is>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="E13" s="33" t="n">
         <v>46224</v>
       </c>
       <c r="F13" s="26" t="n">
@@ -3399,7 +3487,7 @@
           <t>CDL SAO PAULO</t>
         </is>
       </c>
-      <c r="B14" s="25" t="n">
+      <c r="B14" s="33" t="n">
         <v>46203.93840277778</v>
       </c>
       <c r="C14" s="26" t="n">
@@ -3410,7 +3498,7 @@
           <t xml:space="preserve">HORTIFRUTI POMAR DA VILA E MERCEARIA LTDA </t>
         </is>
       </c>
-      <c r="E14" s="25" t="n">
+      <c r="E14" s="33" t="n">
         <v>46205</v>
       </c>
       <c r="F14" s="26" t="n">
@@ -3429,7 +3517,7 @@
           <t>CDL SAO PAULO</t>
         </is>
       </c>
-      <c r="B15" s="25" t="n">
+      <c r="B15" s="33" t="n">
         <v>46209.88335648148</v>
       </c>
       <c r="C15" s="26" t="n">
@@ -3440,7 +3528,7 @@
           <t>CHAME ATAC.</t>
         </is>
       </c>
-      <c r="E15" s="25" t="n">
+      <c r="E15" s="33" t="n">
         <v>46219</v>
       </c>
       <c r="F15" s="26" t="n">
@@ -3459,7 +3547,7 @@
           <t>EBAZAR.COM.BR. LTDA</t>
         </is>
       </c>
-      <c r="B16" s="25" t="n">
+      <c r="B16" s="33" t="n">
         <v>46219.63215277778</v>
       </c>
       <c r="C16" s="26" t="n">
@@ -3470,7 +3558,7 @@
           <t xml:space="preserve">HORTIFRUTI POMAR DA VILA E MERCEARIA LTDA </t>
         </is>
       </c>
-      <c r="E16" s="25" t="n">
+      <c r="E16" s="33" t="n">
         <v>46227</v>
       </c>
       <c r="F16" s="26" t="n">
@@ -3489,7 +3577,7 @@
           <t>EBAZAR.COM.BR. LTDA</t>
         </is>
       </c>
-      <c r="B17" s="25" t="n">
+      <c r="B17" s="33" t="n">
         <v>46219.63291666667</v>
       </c>
       <c r="C17" s="26" t="n">
@@ -3500,7 +3588,7 @@
           <t>MERCADO LIVRE</t>
         </is>
       </c>
-      <c r="E17" s="25" t="n">
+      <c r="E17" s="33" t="n">
         <v>46225</v>
       </c>
       <c r="F17" s="26" t="n">
@@ -3519,7 +3607,7 @@
           <t>EBAZAR.COM.BR. LTDA</t>
         </is>
       </c>
-      <c r="B18" s="25" t="n">
+      <c r="B18" s="33" t="n">
         <v>46219.63386574074</v>
       </c>
       <c r="C18" s="26" t="n">
@@ -3530,7 +3618,7 @@
           <t>MERCADO LIVRE</t>
         </is>
       </c>
-      <c r="E18" s="25" t="n">
+      <c r="E18" s="33" t="n">
         <v>46219</v>
       </c>
       <c r="F18" s="26" t="n">
@@ -3549,7 +3637,7 @@
           <t>CDL SAO PAULO</t>
         </is>
       </c>
-      <c r="B19" s="25" t="n">
+      <c r="B19" s="33" t="n">
         <v>46209.88335648148</v>
       </c>
       <c r="C19" s="26" t="n">
@@ -3560,7 +3648,7 @@
           <t>TL DISTRIBUIDORA</t>
         </is>
       </c>
-      <c r="E19" s="25" t="n">
+      <c r="E19" s="33" t="n">
         <v>46219</v>
       </c>
       <c r="F19" s="26" t="n">
@@ -3579,7 +3667,7 @@
           <t>CDL SAO PAULO</t>
         </is>
       </c>
-      <c r="B20" s="25" t="n">
+      <c r="B20" s="33" t="n">
         <v>46209.88335648148</v>
       </c>
       <c r="C20" s="26" t="n">
@@ -3590,7 +3678,7 @@
           <t xml:space="preserve">UBER </t>
         </is>
       </c>
-      <c r="E20" s="25" t="n">
+      <c r="E20" s="33" t="n">
         <v>46204</v>
       </c>
       <c r="F20" s="26" t="n">
@@ -3609,7 +3697,7 @@
           <t>CDL SAO PAULO</t>
         </is>
       </c>
-      <c r="B21" s="25" t="n">
+      <c r="B21" s="33" t="n">
         <v>46216.91094907407</v>
       </c>
       <c r="C21" s="26" t="n">
@@ -3620,7 +3708,7 @@
           <t xml:space="preserve">HORTIFRUTI POMAR DA VILA E MERCEARIA LTDA </t>
         </is>
       </c>
-      <c r="E21" s="25" t="n">
+      <c r="E21" s="33" t="n">
         <v>46224</v>
       </c>
       <c r="F21" s="26" t="n">
@@ -3639,7 +3727,7 @@
           <t>TL DISTRIBUIDORA</t>
         </is>
       </c>
-      <c r="B22" s="25" t="n">
+      <c r="B22" s="33" t="n">
         <v>46230.42800925926</v>
       </c>
       <c r="C22" s="26" t="n">
@@ -3650,7 +3738,7 @@
           <t xml:space="preserve">HORTIFRUTI POMAR DA VILA E MERCEARIA LTDA </t>
         </is>
       </c>
-      <c r="E22" s="25" t="n">
+      <c r="E22" s="33" t="n">
         <v>46228</v>
       </c>
       <c r="F22" s="26" t="n">
@@ -3669,7 +3757,7 @@
           <t>CDL SAO PAULO</t>
         </is>
       </c>
-      <c r="B23" s="25" t="n">
+      <c r="B23" s="33" t="n">
         <v>46216.91094907407</v>
       </c>
       <c r="C23" s="26" t="n">
@@ -3680,7 +3768,7 @@
           <t>DEPOSITO LA TERZA</t>
         </is>
       </c>
-      <c r="E23" s="25" t="n">
+      <c r="E23" s="33" t="n">
         <v>46225</v>
       </c>
       <c r="F23" s="26" t="n">
@@ -3747,7 +3835,7 @@
           <t>KHADUN B. LIMA</t>
         </is>
       </c>
-      <c r="B2" s="18" t="n">
+      <c r="B2" s="30" t="n">
         <v>46218</v>
       </c>
       <c r="C2" s="19" t="n">
@@ -3770,7 +3858,7 @@
           <t>KHADUN B. LIMA</t>
         </is>
       </c>
-      <c r="B3" s="18" t="n">
+      <c r="B3" s="30" t="n">
         <v>46218</v>
       </c>
       <c r="C3" s="19" t="n">
@@ -3793,7 +3881,7 @@
           <t>FABIO ROSOCHASNKY - DELLAS CONECTING</t>
         </is>
       </c>
-      <c r="B4" s="18" t="n">
+      <c r="B4" s="30" t="n">
         <v>46203</v>
       </c>
       <c r="C4" s="19" t="n">
@@ -3816,7 +3904,7 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="30" t="n">
         <v>46203</v>
       </c>
       <c r="C5" s="19" t="n">
@@ -3839,7 +3927,7 @@
           <t>EBAZAR.COM.BR.LTDA</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="30" t="n">
         <v>46219</v>
       </c>
       <c r="C6" s="19" t="n">
@@ -3862,7 +3950,7 @@
           <t>EBAZAR.COM.BR.LTDA</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="30" t="n">
         <v>46219</v>
       </c>
       <c r="C7" s="19" t="n">
@@ -3885,7 +3973,7 @@
           <t>EBAZAR.COM.BR.LTDA</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="30" t="n">
         <v>46219</v>
       </c>
       <c r="C8" s="19" t="n">
@@ -3908,7 +3996,7 @@
           <t>EBAZAR.COM.BR.LTDA</t>
         </is>
       </c>
-      <c r="B9" s="18" t="n">
+      <c r="B9" s="30" t="n">
         <v>46219</v>
       </c>
       <c r="C9" s="19" t="n">
@@ -3931,7 +4019,7 @@
           <t>EBAZAR.COM.BR.LTDA</t>
         </is>
       </c>
-      <c r="B10" s="18" t="n">
+      <c r="B10" s="30" t="n">
         <v>46219</v>
       </c>
       <c r="C10" s="19" t="n">
@@ -3954,7 +4042,7 @@
           <t>EBAZAR.COM.BR.LTDA</t>
         </is>
       </c>
-      <c r="B11" s="18" t="n">
+      <c r="B11" s="30" t="n">
         <v>46219</v>
       </c>
       <c r="C11" s="19" t="n">
@@ -4026,7 +4114,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="n">
+      <c r="A2" s="32" t="n">
         <v>46234</v>
       </c>
       <c r="B2" s="21" t="inlineStr">
@@ -4054,7 +4142,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="n">
+      <c r="A3" s="32" t="n">
         <v>46175</v>
       </c>
       <c r="B3" s="21" t="inlineStr">
@@ -4082,7 +4170,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="n">
+      <c r="A4" s="32" t="n">
         <v>46224</v>
       </c>
       <c r="B4" s="21" t="inlineStr">
@@ -4106,7 +4194,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="n">
+      <c r="A5" s="32" t="n">
         <v>45974</v>
       </c>
       <c r="B5" s="21" t="inlineStr">
@@ -4134,7 +4222,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="n">
+      <c r="A6" s="32" t="n">
         <v>46209</v>
       </c>
       <c r="B6" s="21" t="inlineStr">
@@ -4158,7 +4246,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="n">
+      <c r="A7" s="32" t="n">
         <v>46225</v>
       </c>
       <c r="B7" s="21" t="inlineStr">
@@ -4182,7 +4270,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="n">
+      <c r="A8" s="32" t="n">
         <v>46228</v>
       </c>
       <c r="B8" s="21" t="inlineStr">
@@ -4206,7 +4294,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="n">
+      <c r="A9" s="32" t="n">
         <v>46229</v>
       </c>
       <c r="B9" s="21" t="inlineStr">
@@ -4230,7 +4318,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="n">
+      <c r="A10" s="32" t="n">
         <v>46204</v>
       </c>
       <c r="B10" s="21" t="inlineStr">
@@ -4254,7 +4342,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="n">
+      <c r="A11" s="32" t="n">
         <v>46225</v>
       </c>
       <c r="B11" s="21" t="inlineStr">
@@ -4278,7 +4366,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="n">
+      <c r="A12" s="32" t="n">
         <v>46234</v>
       </c>
       <c r="B12" s="21" t="inlineStr">
@@ -4302,7 +4390,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="n">
+      <c r="A13" s="32" t="n">
         <v>46206</v>
       </c>
       <c r="B13" s="21" t="inlineStr">
@@ -4326,7 +4414,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="n">
+      <c r="A14" s="32" t="n">
         <v>46226</v>
       </c>
       <c r="B14" s="21" t="inlineStr">
@@ -4350,7 +4438,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="n">
+      <c r="A15" s="32" t="n">
         <v>46219</v>
       </c>
       <c r="B15" s="21" t="inlineStr">
@@ -4374,7 +4462,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="n">
+      <c r="A16" s="32" t="n">
         <v>46204</v>
       </c>
       <c r="B16" s="21" t="inlineStr">
@@ -4398,7 +4486,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="30" t="n">
         <v>46218</v>
       </c>
       <c r="B17" s="17" t="inlineStr">
@@ -4422,7 +4510,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="n">
+      <c r="A18" s="34" t="n">
         <v>46233</v>
       </c>
       <c r="B18" s="28" t="inlineStr">
@@ -4446,7 +4534,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="n">
+      <c r="A19" s="34" t="n">
         <v>46228</v>
       </c>
       <c r="B19" s="28" t="inlineStr">
@@ -4470,7 +4558,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="n">
+      <c r="A20" s="34" t="n">
         <v>46224</v>
       </c>
       <c r="B20" s="28" t="inlineStr">
@@ -4494,7 +4582,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="n">
+      <c r="A21" s="34" t="n">
         <v>46220</v>
       </c>
       <c r="B21" s="28" t="inlineStr">
@@ -4518,7 +4606,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="n">
+      <c r="A22" s="34" t="n">
         <v>46214</v>
       </c>
       <c r="B22" s="28" t="inlineStr">
@@ -4542,7 +4630,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="n">
+      <c r="A23" s="34" t="n">
         <v>46204</v>
       </c>
       <c r="B23" s="28" t="inlineStr">
@@ -4566,7 +4654,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="27" t="n">
+      <c r="A24" s="34" t="n">
         <v>46204</v>
       </c>
       <c r="B24" s="28" t="inlineStr">
@@ -4590,7 +4678,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="27" t="n">
+      <c r="A25" s="34" t="n">
         <v>46222</v>
       </c>
       <c r="B25" s="28" t="inlineStr">
@@ -4614,7 +4702,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="n">
+      <c r="A26" s="34" t="n">
         <v>46216</v>
       </c>
       <c r="B26" s="28" t="inlineStr">
@@ -4638,7 +4726,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="27" t="n">
+      <c r="A27" s="34" t="n">
         <v>46216</v>
       </c>
       <c r="B27" s="28" t="inlineStr">
@@ -4662,7 +4750,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="27" t="n">
+      <c r="A28" s="34" t="n">
         <v>46216</v>
       </c>
       <c r="B28" s="28" t="inlineStr">
@@ -4686,7 +4774,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="27" t="n">
+      <c r="A29" s="34" t="n">
         <v>46216</v>
       </c>
       <c r="B29" s="28" t="inlineStr">
@@ -4710,7 +4798,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="27" t="n">
+      <c r="A30" s="34" t="n">
         <v>46216</v>
       </c>
       <c r="B30" s="28" t="inlineStr">
@@ -4734,7 +4822,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="27" t="n">
+      <c r="A31" s="34" t="n">
         <v>46216</v>
       </c>
       <c r="B31" s="28" t="inlineStr">
@@ -4758,7 +4846,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="27" t="n">
+      <c r="A32" s="34" t="n">
         <v>46219</v>
       </c>
       <c r="B32" s="28" t="inlineStr">
@@ -4782,7 +4870,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="27" t="n">
+      <c r="A33" s="34" t="n">
         <v>46207</v>
       </c>
       <c r="B33" s="28" t="inlineStr">
@@ -4806,7 +4894,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="27" t="n">
+      <c r="A34" s="34" t="n">
         <v>46211</v>
       </c>
       <c r="B34" s="28" t="inlineStr">
@@ -4830,7 +4918,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="27" t="n">
+      <c r="A35" s="34" t="n">
         <v>46180</v>
       </c>
       <c r="B35" s="28" t="inlineStr">
@@ -4858,7 +4946,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="27" t="n">
+      <c r="A36" s="34" t="n">
         <v>46177</v>
       </c>
       <c r="B36" s="28" t="inlineStr">
@@ -4886,7 +4974,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="27" t="n">
+      <c r="A37" s="34" t="n">
         <v>46211</v>
       </c>
       <c r="B37" s="28" t="inlineStr">
@@ -4910,7 +4998,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="27" t="n">
+      <c r="A38" s="34" t="n">
         <v>46234</v>
       </c>
       <c r="B38" s="28" t="inlineStr">
@@ -4934,7 +5022,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="27" t="n">
+      <c r="A39" s="34" t="n">
         <v>46233</v>
       </c>
       <c r="B39" s="28" t="inlineStr">
@@ -4958,7 +5046,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="27" t="n">
+      <c r="A40" s="34" t="n">
         <v>46232</v>
       </c>
       <c r="B40" s="28" t="inlineStr">
@@ -4982,7 +5070,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="27" t="n">
+      <c r="A41" s="34" t="n">
         <v>46231</v>
       </c>
       <c r="B41" s="28" t="inlineStr">
@@ -5006,7 +5094,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="27" t="n">
+      <c r="A42" s="34" t="n">
         <v>46230</v>
       </c>
       <c r="B42" s="28" t="inlineStr">
@@ -5030,7 +5118,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="27" t="n">
+      <c r="A43" s="34" t="n">
         <v>46229</v>
       </c>
       <c r="B43" s="28" t="inlineStr">
@@ -5054,7 +5142,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="27" t="n">
+      <c r="A44" s="34" t="n">
         <v>46228</v>
       </c>
       <c r="B44" s="28" t="inlineStr">
@@ -5078,7 +5166,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="27" t="n">
+      <c r="A45" s="34" t="n">
         <v>46227</v>
       </c>
       <c r="B45" s="28" t="inlineStr">
@@ -5102,7 +5190,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="27" t="n">
+      <c r="A46" s="34" t="n">
         <v>46226</v>
       </c>
       <c r="B46" s="28" t="inlineStr">
@@ -5126,7 +5214,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="27" t="n">
+      <c r="A47" s="34" t="n">
         <v>46225</v>
       </c>
       <c r="B47" s="28" t="inlineStr">
@@ -5150,7 +5238,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="27" t="n">
+      <c r="A48" s="34" t="n">
         <v>46224</v>
       </c>
       <c r="B48" s="28" t="inlineStr">
@@ -5174,7 +5262,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="27" t="n">
+      <c r="A49" s="34" t="n">
         <v>46223</v>
       </c>
       <c r="B49" s="28" t="inlineStr">
@@ -5198,7 +5286,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="27" t="n">
+      <c r="A50" s="34" t="n">
         <v>46222</v>
       </c>
       <c r="B50" s="28" t="inlineStr">
@@ -5222,7 +5310,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="27" t="n">
+      <c r="A51" s="34" t="n">
         <v>46221</v>
       </c>
       <c r="B51" s="28" t="inlineStr">
@@ -5246,7 +5334,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="27" t="n">
+      <c r="A52" s="34" t="n">
         <v>46220</v>
       </c>
       <c r="B52" s="28" t="inlineStr">
@@ -5270,7 +5358,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="27" t="n">
+      <c r="A53" s="34" t="n">
         <v>46219</v>
       </c>
       <c r="B53" s="28" t="inlineStr">
@@ -5294,7 +5382,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="27" t="n">
+      <c r="A54" s="34" t="n">
         <v>46218</v>
       </c>
       <c r="B54" s="28" t="inlineStr">
@@ -5318,7 +5406,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="27" t="n">
+      <c r="A55" s="34" t="n">
         <v>46216</v>
       </c>
       <c r="B55" s="28" t="inlineStr">
@@ -5342,7 +5430,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="27" t="n">
+      <c r="A56" s="34" t="n">
         <v>46215</v>
       </c>
       <c r="B56" s="28" t="inlineStr">
@@ -5366,7 +5454,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="27" t="n">
+      <c r="A57" s="34" t="n">
         <v>46214</v>
       </c>
       <c r="B57" s="28" t="inlineStr">
@@ -5390,7 +5478,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="27" t="n">
+      <c r="A58" s="34" t="n">
         <v>46213</v>
       </c>
       <c r="B58" s="28" t="inlineStr">
@@ -5414,7 +5502,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="27" t="n">
+      <c r="A59" s="34" t="n">
         <v>46212</v>
       </c>
       <c r="B59" s="28" t="inlineStr">
@@ -5438,7 +5526,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="27" t="n">
+      <c r="A60" s="34" t="n">
         <v>46211</v>
       </c>
       <c r="B60" s="28" t="inlineStr">
@@ -5462,7 +5550,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="27" t="n">
+      <c r="A61" s="34" t="n">
         <v>46210</v>
       </c>
       <c r="B61" s="28" t="inlineStr">
@@ -5486,7 +5574,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="27" t="n">
+      <c r="A62" s="34" t="n">
         <v>46209</v>
       </c>
       <c r="B62" s="28" t="inlineStr">
@@ -5510,7 +5598,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="27" t="n">
+      <c r="A63" s="34" t="n">
         <v>46208</v>
       </c>
       <c r="B63" s="28" t="inlineStr">
@@ -5534,7 +5622,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="27" t="n">
+      <c r="A64" s="34" t="n">
         <v>46207</v>
       </c>
       <c r="B64" s="28" t="inlineStr">
@@ -5558,7 +5646,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="27" t="n">
+      <c r="A65" s="34" t="n">
         <v>46206</v>
       </c>
       <c r="B65" s="28" t="inlineStr">
@@ -5582,7 +5670,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="27" t="n">
+      <c r="A66" s="34" t="n">
         <v>46205</v>
       </c>
       <c r="B66" s="28" t="inlineStr">
@@ -5606,7 +5694,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="27" t="n">
+      <c r="A67" s="34" t="n">
         <v>46204</v>
       </c>
       <c r="B67" s="28" t="inlineStr">
@@ -5630,7 +5718,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="27" t="n">
+      <c r="A68" s="34" t="n">
         <v>46234</v>
       </c>
       <c r="B68" s="28" t="inlineStr">
@@ -5654,7 +5742,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="27" t="n">
+      <c r="A69" s="34" t="n">
         <v>46205</v>
       </c>
       <c r="B69" s="28" t="inlineStr">
@@ -5678,7 +5766,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="27" t="n">
+      <c r="A70" s="34" t="n">
         <v>46208</v>
       </c>
       <c r="B70" s="28" t="inlineStr">
@@ -5702,7 +5790,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="27" t="n">
+      <c r="A71" s="34" t="n">
         <v>46208</v>
       </c>
       <c r="B71" s="28" t="inlineStr">
@@ -5726,7 +5814,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="27" t="n">
+      <c r="A72" s="34" t="n">
         <v>46208</v>
       </c>
       <c r="B72" s="28" t="inlineStr">
@@ -5750,7 +5838,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="27" t="n">
+      <c r="A73" s="34" t="n">
         <v>46209</v>
       </c>
       <c r="B73" s="28" t="inlineStr">
@@ -5774,7 +5862,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="27" t="n">
+      <c r="A74" s="34" t="n">
         <v>46209</v>
       </c>
       <c r="B74" s="28" t="inlineStr">
@@ -5798,7 +5886,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="27" t="n">
+      <c r="A75" s="34" t="n">
         <v>46211</v>
       </c>
       <c r="B75" s="28" t="inlineStr">
@@ -5822,7 +5910,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="27" t="n">
+      <c r="A76" s="34" t="n">
         <v>46232</v>
       </c>
       <c r="B76" s="28" t="inlineStr">
@@ -5846,7 +5934,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="27" t="n">
+      <c r="A77" s="34" t="n">
         <v>46204</v>
       </c>
       <c r="B77" s="28" t="inlineStr">
@@ -5870,7 +5958,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="27" t="n">
+      <c r="A78" s="34" t="n">
         <v>46204</v>
       </c>
       <c r="B78" s="28" t="inlineStr">
@@ -5894,7 +5982,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="27" t="n">
+      <c r="A79" s="34" t="n">
         <v>46216</v>
       </c>
       <c r="B79" s="28" t="inlineStr">
@@ -5918,7 +6006,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="27" t="n">
+      <c r="A80" s="34" t="n">
         <v>46219</v>
       </c>
       <c r="B80" s="28" t="inlineStr">
@@ -5942,7 +6030,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="27" t="n">
+      <c r="A81" s="34" t="n">
         <v>46208</v>
       </c>
       <c r="B81" s="28" t="inlineStr">
@@ -5966,7 +6054,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="27" t="n">
+      <c r="A82" s="34" t="n">
         <v>46222</v>
       </c>
       <c r="B82" s="28" t="inlineStr">
@@ -5990,7 +6078,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="27" t="n">
+      <c r="A83" s="34" t="n">
         <v>46215</v>
       </c>
       <c r="B83" s="28" t="inlineStr">
@@ -6014,7 +6102,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="27" t="n">
+      <c r="A84" s="34" t="n">
         <v>46229</v>
       </c>
       <c r="B84" s="28" t="inlineStr">
@@ -6038,7 +6126,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="27" t="n">
+      <c r="A85" s="34" t="n">
         <v>46216</v>
       </c>
       <c r="B85" s="28" t="inlineStr">
@@ -6062,7 +6150,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="27" t="n">
+      <c r="A86" s="34" t="n">
         <v>46203</v>
       </c>
       <c r="B86" s="28" t="inlineStr">
@@ -6086,7 +6174,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="27" t="n">
+      <c r="A87" s="34" t="n">
         <v>46223</v>
       </c>
       <c r="B87" s="28" t="inlineStr">
@@ -6110,7 +6198,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="27" t="n">
+      <c r="A88" s="34" t="n">
         <v>46225</v>
       </c>
       <c r="B88" s="28" t="inlineStr">
@@ -6134,7 +6222,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="27" t="n">
+      <c r="A89" s="34" t="n">
         <v>46219</v>
       </c>
       <c r="B89" s="28" t="inlineStr">
@@ -6158,7 +6246,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="27" t="n">
+      <c r="A90" s="34" t="n">
         <v>46210</v>
       </c>
       <c r="B90" s="28" t="inlineStr">
@@ -6182,7 +6270,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="27" t="n">
+      <c r="A91" s="34" t="n">
         <v>46219</v>
       </c>
       <c r="B91" s="28" t="inlineStr">
@@ -6206,7 +6294,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="27" t="n">
+      <c r="A92" s="34" t="n">
         <v>46204</v>
       </c>
       <c r="B92" s="28" t="inlineStr">
@@ -6230,7 +6318,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="27" t="n">
+      <c r="A93" s="34" t="n">
         <v>46203</v>
       </c>
       <c r="B93" s="28" t="inlineStr">
@@ -6254,7 +6342,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="27" t="n">
+      <c r="A94" s="34" t="n">
         <v>46207</v>
       </c>
       <c r="B94" s="28" t="inlineStr">
@@ -6278,7 +6366,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="27" t="n">
+      <c r="A95" s="34" t="n">
         <v>46206</v>
       </c>
       <c r="B95" s="28" t="inlineStr">
@@ -6302,7 +6390,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="27" t="n">
+      <c r="A96" s="34" t="n">
         <v>46208</v>
       </c>
       <c r="B96" s="28" t="inlineStr">
@@ -6326,7 +6414,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="27" t="n">
+      <c r="A97" s="34" t="n">
         <v>46219</v>
       </c>
       <c r="B97" s="28" t="inlineStr">
@@ -6404,7 +6492,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="n">
+      <c r="A2" s="34" t="n">
         <v>46216</v>
       </c>
       <c r="B2" s="28" t="inlineStr">
@@ -6428,7 +6516,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="27" t="n">
+      <c r="A3" s="34" t="n">
         <v>46236</v>
       </c>
       <c r="B3" s="28" t="inlineStr">
@@ -6452,7 +6540,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="27" t="n">
+      <c r="A4" s="34" t="n">
         <v>46236</v>
       </c>
       <c r="B4" s="28" t="inlineStr">
@@ -6476,7 +6564,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="n">
+      <c r="A5" s="31" t="n">
         <v>46234</v>
       </c>
       <c r="B5" s="14" t="inlineStr">
@@ -6500,7 +6588,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="31" t="n">
         <v>46234</v>
       </c>
       <c r="B6" s="14" t="inlineStr">
@@ -6524,7 +6612,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="n">
+      <c r="A7" s="31" t="n">
         <v>46234</v>
       </c>
       <c r="B7" s="14" t="inlineStr">
@@ -6548,7 +6636,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="31" t="n">
         <v>46234</v>
       </c>
       <c r="B8" s="14" t="inlineStr">
@@ -6572,7 +6660,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="n">
+      <c r="A9" s="31" t="n">
         <v>46234</v>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -6596,7 +6684,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="31" t="n">
         <v>46234</v>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6620,7 +6708,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="n">
+      <c r="A11" s="31" t="n">
         <v>46234</v>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6644,7 +6732,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="31" t="n">
         <v>46234</v>
       </c>
       <c r="B12" s="14" t="inlineStr">
@@ -6668,7 +6756,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="n">
+      <c r="A13" s="31" t="n">
         <v>46234</v>
       </c>
       <c r="B13" s="14" t="inlineStr">
@@ -6692,7 +6780,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="31" t="n">
         <v>46234</v>
       </c>
       <c r="B14" s="14" t="inlineStr">
@@ -6716,7 +6804,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="n">
+      <c r="A15" s="31" t="n">
         <v>46234</v>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -6740,7 +6828,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="n">
+      <c r="A16" s="31" t="n">
         <v>46234</v>
       </c>
       <c r="B16" s="14" t="inlineStr">
@@ -6764,7 +6852,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="n">
+      <c r="A17" s="31" t="n">
         <v>46234</v>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -6788,7 +6876,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="n">
+      <c r="A18" s="31" t="n">
         <v>46234</v>
       </c>
       <c r="B18" s="14" t="inlineStr">
@@ -6812,7 +6900,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="n">
+      <c r="A19" s="31" t="n">
         <v>46234</v>
       </c>
       <c r="B19" s="14" t="inlineStr">
@@ -6836,7 +6924,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="n">
+      <c r="A20" s="31" t="n">
         <v>46234</v>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -6860,7 +6948,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="n">
+      <c r="A21" s="31" t="n">
         <v>46234</v>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -6884,7 +6972,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="n">
+      <c r="A22" s="34" t="n">
         <v>46234</v>
       </c>
       <c r="B22" s="28" t="inlineStr">
@@ -6908,7 +6996,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="n">
+      <c r="A23" s="31" t="n">
         <v>46234</v>
       </c>
       <c r="B23" s="14" t="inlineStr">
@@ -6936,7 +7024,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="n">
+      <c r="A24" s="31" t="n">
         <v>46234</v>
       </c>
       <c r="B24" s="14" t="inlineStr">
@@ -6960,7 +7048,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="n">
+      <c r="A25" s="31" t="n">
         <v>46234</v>
       </c>
       <c r="B25" s="14" t="inlineStr">
@@ -6984,7 +7072,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="n">
+      <c r="A26" s="31" t="n">
         <v>46234</v>
       </c>
       <c r="B26" s="14" t="inlineStr">
@@ -7008,7 +7096,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="n">
+      <c r="A27" s="31" t="n">
         <v>46233</v>
       </c>
       <c r="B27" s="14" t="inlineStr">
@@ -7032,7 +7120,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="27" t="n">
+      <c r="A28" s="34" t="n">
         <v>46233</v>
       </c>
       <c r="B28" s="28" t="inlineStr">
@@ -7056,7 +7144,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="n">
+      <c r="A29" s="31" t="n">
         <v>46233</v>
       </c>
       <c r="B29" s="14" t="inlineStr">
@@ -7080,7 +7168,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="n">
+      <c r="A30" s="31" t="n">
         <v>46232</v>
       </c>
       <c r="B30" s="14" t="inlineStr">
@@ -7104,7 +7192,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="n">
+      <c r="A31" s="31" t="n">
         <v>46232</v>
       </c>
       <c r="B31" s="14" t="inlineStr">
@@ -7128,7 +7216,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="20" t="n">
+      <c r="A32" s="31" t="n">
         <v>46232</v>
       </c>
       <c r="B32" s="14" t="inlineStr">
@@ -7152,7 +7240,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="20" t="n">
+      <c r="A33" s="31" t="n">
         <v>46232</v>
       </c>
       <c r="B33" s="14" t="inlineStr">
@@ -7176,7 +7264,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="n">
+      <c r="A34" s="31" t="n">
         <v>46232</v>
       </c>
       <c r="B34" s="14" t="inlineStr">
@@ -7200,7 +7288,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="20" t="n">
+      <c r="A35" s="31" t="n">
         <v>46231</v>
       </c>
       <c r="B35" s="14" t="inlineStr">
@@ -7224,7 +7312,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="20" t="n">
+      <c r="A36" s="31" t="n">
         <v>46231</v>
       </c>
       <c r="B36" s="14" t="inlineStr">
@@ -7248,7 +7336,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="20" t="n">
+      <c r="A37" s="31" t="n">
         <v>46231</v>
       </c>
       <c r="B37" s="14" t="inlineStr">
@@ -7272,7 +7360,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="20" t="n">
+      <c r="A38" s="31" t="n">
         <v>46231</v>
       </c>
       <c r="B38" s="14" t="inlineStr">
@@ -7296,7 +7384,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="n">
+      <c r="A39" s="31" t="n">
         <v>46231</v>
       </c>
       <c r="B39" s="14" t="inlineStr">
@@ -7320,7 +7408,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="20" t="n">
+      <c r="A40" s="31" t="n">
         <v>46231</v>
       </c>
       <c r="B40" s="14" t="inlineStr">
@@ -7344,7 +7432,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="20" t="n">
+      <c r="A41" s="31" t="n">
         <v>46230</v>
       </c>
       <c r="B41" s="14" t="inlineStr">
@@ -7368,7 +7456,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="20" t="n">
+      <c r="A42" s="31" t="n">
         <v>46230</v>
       </c>
       <c r="B42" s="14" t="inlineStr">
@@ -7392,7 +7480,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="27" t="n">
+      <c r="A43" s="34" t="n">
         <v>46230</v>
       </c>
       <c r="B43" s="28" t="inlineStr">
@@ -7416,7 +7504,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="27" t="n">
+      <c r="A44" s="34" t="n">
         <v>46230</v>
       </c>
       <c r="B44" s="28" t="inlineStr">
@@ -7440,7 +7528,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="20" t="n">
+      <c r="A45" s="31" t="n">
         <v>46229</v>
       </c>
       <c r="B45" s="14" t="inlineStr">
@@ -7464,7 +7552,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="20" t="n">
+      <c r="A46" s="31" t="n">
         <v>46229</v>
       </c>
       <c r="B46" s="14" t="inlineStr">
@@ -7488,7 +7576,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="20" t="n">
+      <c r="A47" s="31" t="n">
         <v>46229</v>
       </c>
       <c r="B47" s="14" t="inlineStr">
@@ -7512,7 +7600,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="20" t="n">
+      <c r="A48" s="31" t="n">
         <v>46228</v>
       </c>
       <c r="B48" s="14" t="inlineStr">
@@ -7536,7 +7624,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="20" t="n">
+      <c r="A49" s="31" t="n">
         <v>46228</v>
       </c>
       <c r="B49" s="14" t="inlineStr">
@@ -7560,7 +7648,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="20" t="n">
+      <c r="A50" s="31" t="n">
         <v>46228</v>
       </c>
       <c r="B50" s="14" t="inlineStr">
@@ -7584,7 +7672,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="20" t="n">
+      <c r="A51" s="31" t="n">
         <v>46227</v>
       </c>
       <c r="B51" s="14" t="inlineStr">
@@ -7608,7 +7696,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="20" t="n">
+      <c r="A52" s="31" t="n">
         <v>46226</v>
       </c>
       <c r="B52" s="14" t="inlineStr">
@@ -7632,7 +7720,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="20" t="n">
+      <c r="A53" s="31" t="n">
         <v>46226</v>
       </c>
       <c r="B53" s="14" t="inlineStr">
@@ -7656,7 +7744,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="20" t="n">
+      <c r="A54" s="31" t="n">
         <v>46226</v>
       </c>
       <c r="B54" s="14" t="inlineStr">
@@ -7680,7 +7768,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="20" t="n">
+      <c r="A55" s="31" t="n">
         <v>46225</v>
       </c>
       <c r="B55" s="14" t="inlineStr">
@@ -7704,7 +7792,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="20" t="n">
+      <c r="A56" s="31" t="n">
         <v>46225</v>
       </c>
       <c r="B56" s="14" t="inlineStr">
@@ -7728,7 +7816,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="20" t="n">
+      <c r="A57" s="31" t="n">
         <v>46225</v>
       </c>
       <c r="B57" s="14" t="inlineStr">
@@ -7752,7 +7840,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="20" t="n">
+      <c r="A58" s="31" t="n">
         <v>46225</v>
       </c>
       <c r="B58" s="14" t="inlineStr">
@@ -7776,7 +7864,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="20" t="n">
+      <c r="A59" s="31" t="n">
         <v>46225</v>
       </c>
       <c r="B59" s="14" t="inlineStr">
@@ -7800,7 +7888,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="20" t="n">
+      <c r="A60" s="31" t="n">
         <v>46225</v>
       </c>
       <c r="B60" s="14" t="inlineStr">
@@ -7824,7 +7912,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="20" t="n">
+      <c r="A61" s="31" t="n">
         <v>46225</v>
       </c>
       <c r="B61" s="14" t="inlineStr">
@@ -7848,7 +7936,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="20" t="n">
+      <c r="A62" s="31" t="n">
         <v>46225</v>
       </c>
       <c r="B62" s="14" t="inlineStr">
@@ -7872,7 +7960,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="20" t="n">
+      <c r="A63" s="31" t="n">
         <v>46224</v>
       </c>
       <c r="B63" s="14" t="inlineStr">
@@ -7896,7 +7984,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="20" t="n">
+      <c r="A64" s="31" t="n">
         <v>46224</v>
       </c>
       <c r="B64" s="14" t="inlineStr">
@@ -7920,7 +8008,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="20" t="n">
+      <c r="A65" s="31" t="n">
         <v>46224</v>
       </c>
       <c r="B65" s="14" t="inlineStr">
@@ -7944,7 +8032,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="20" t="n">
+      <c r="A66" s="31" t="n">
         <v>46224</v>
       </c>
       <c r="B66" s="14" t="inlineStr">
@@ -7968,7 +8056,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="20" t="n">
+      <c r="A67" s="31" t="n">
         <v>46224</v>
       </c>
       <c r="B67" s="14" t="inlineStr">
@@ -7992,7 +8080,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="20" t="n">
+      <c r="A68" s="31" t="n">
         <v>46223</v>
       </c>
       <c r="B68" s="14" t="inlineStr">
@@ -8016,7 +8104,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="27" t="n">
+      <c r="A69" s="34" t="n">
         <v>46223</v>
       </c>
       <c r="B69" s="28" t="inlineStr">
@@ -8040,7 +8128,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="27" t="n">
+      <c r="A70" s="34" t="n">
         <v>46223</v>
       </c>
       <c r="B70" s="28" t="inlineStr">
@@ -8064,7 +8152,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="20" t="n">
+      <c r="A71" s="31" t="n">
         <v>46223</v>
       </c>
       <c r="B71" s="14" t="inlineStr">
@@ -8088,7 +8176,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="20" t="n">
+      <c r="A72" s="31" t="n">
         <v>46222</v>
       </c>
       <c r="B72" s="14" t="inlineStr">
@@ -8112,7 +8200,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="20" t="n">
+      <c r="A73" s="31" t="n">
         <v>46222</v>
       </c>
       <c r="B73" s="14" t="inlineStr">
@@ -8136,7 +8224,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="20" t="n">
+      <c r="A74" s="31" t="n">
         <v>46222</v>
       </c>
       <c r="B74" s="14" t="inlineStr">
@@ -8160,7 +8248,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="20" t="n">
+      <c r="A75" s="31" t="n">
         <v>46221</v>
       </c>
       <c r="B75" s="14" t="inlineStr">
@@ -8184,7 +8272,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="20" t="n">
+      <c r="A76" s="31" t="n">
         <v>46220</v>
       </c>
       <c r="B76" s="14" t="inlineStr">
@@ -8208,7 +8296,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="20" t="n">
+      <c r="A77" s="31" t="n">
         <v>46220</v>
       </c>
       <c r="B77" s="14" t="inlineStr">
@@ -8232,7 +8320,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="20" t="n">
+      <c r="A78" s="31" t="n">
         <v>46219</v>
       </c>
       <c r="B78" s="14" t="inlineStr">
@@ -8256,7 +8344,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="n">
+      <c r="A79" s="31" t="n">
         <v>46219</v>
       </c>
       <c r="B79" s="14" t="inlineStr">
@@ -8280,7 +8368,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="20" t="n">
+      <c r="A80" s="31" t="n">
         <v>46219</v>
       </c>
       <c r="B80" s="14" t="inlineStr">
@@ -8304,7 +8392,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="20" t="n">
+      <c r="A81" s="31" t="n">
         <v>46219</v>
       </c>
       <c r="B81" s="14" t="inlineStr">
@@ -8328,7 +8416,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="20" t="n">
+      <c r="A82" s="31" t="n">
         <v>46219</v>
       </c>
       <c r="B82" s="14" t="inlineStr">
@@ -8352,7 +8440,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="20" t="n">
+      <c r="A83" s="31" t="n">
         <v>46219</v>
       </c>
       <c r="B83" s="14" t="inlineStr">
@@ -8376,7 +8464,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="n">
+      <c r="A84" s="31" t="n">
         <v>46219</v>
       </c>
       <c r="B84" s="14" t="inlineStr">
@@ -8400,7 +8488,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="n">
+      <c r="A85" s="31" t="n">
         <v>46219</v>
       </c>
       <c r="B85" s="14" t="inlineStr">
@@ -8424,7 +8512,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="20" t="n">
+      <c r="A86" s="31" t="n">
         <v>46219</v>
       </c>
       <c r="B86" s="14" t="inlineStr">
@@ -8448,7 +8536,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="20" t="n">
+      <c r="A87" s="31" t="n">
         <v>46219</v>
       </c>
       <c r="B87" s="14" t="inlineStr">
@@ -8472,7 +8560,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="20" t="n">
+      <c r="A88" s="31" t="n">
         <v>46219</v>
       </c>
       <c r="B88" s="14" t="inlineStr">
@@ -8496,7 +8584,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="20" t="n">
+      <c r="A89" s="31" t="n">
         <v>46219</v>
       </c>
       <c r="B89" s="14" t="inlineStr">
@@ -8520,7 +8608,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="20" t="n">
+      <c r="A90" s="31" t="n">
         <v>46218</v>
       </c>
       <c r="B90" s="14" t="inlineStr">
@@ -8544,7 +8632,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="20" t="n">
+      <c r="A91" s="31" t="n">
         <v>46218</v>
       </c>
       <c r="B91" s="14" t="inlineStr">
@@ -8568,7 +8656,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="20" t="n">
+      <c r="A92" s="31" t="n">
         <v>46218</v>
       </c>
       <c r="B92" s="14" t="inlineStr">
@@ -8592,7 +8680,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="27" t="n">
+      <c r="A93" s="34" t="n">
         <v>46217</v>
       </c>
       <c r="B93" s="28" t="inlineStr">
@@ -8616,7 +8704,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="20" t="n">
+      <c r="A94" s="31" t="n">
         <v>46217</v>
       </c>
       <c r="B94" s="14" t="inlineStr">
@@ -8640,7 +8728,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="27" t="n">
+      <c r="A95" s="34" t="n">
         <v>46217</v>
       </c>
       <c r="B95" s="28" t="inlineStr">
@@ -8664,7 +8752,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="27" t="n">
+      <c r="A96" s="34" t="n">
         <v>46217</v>
       </c>
       <c r="B96" s="28" t="inlineStr">
@@ -8688,7 +8776,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="20" t="n">
+      <c r="A97" s="31" t="n">
         <v>46217</v>
       </c>
       <c r="B97" s="14" t="inlineStr">
@@ -8712,7 +8800,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="27" t="n">
+      <c r="A98" s="34" t="n">
         <v>46217</v>
       </c>
       <c r="B98" s="28" t="inlineStr">
@@ -8736,7 +8824,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="27" t="n">
+      <c r="A99" s="34" t="n">
         <v>46217</v>
       </c>
       <c r="B99" s="28" t="inlineStr">
@@ -8760,7 +8848,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="20" t="n">
+      <c r="A100" s="31" t="n">
         <v>46217</v>
       </c>
       <c r="B100" s="14" t="inlineStr">
@@ -8784,7 +8872,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="27" t="n">
+      <c r="A101" s="34" t="n">
         <v>46217</v>
       </c>
       <c r="B101" s="28" t="inlineStr">
@@ -8808,7 +8896,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="27" t="n">
+      <c r="A102" s="34" t="n">
         <v>46217</v>
       </c>
       <c r="B102" s="28" t="inlineStr">
@@ -8832,7 +8920,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="20" t="n">
+      <c r="A103" s="31" t="n">
         <v>46217</v>
       </c>
       <c r="B103" s="14" t="inlineStr">
@@ -8856,7 +8944,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="27" t="n">
+      <c r="A104" s="34" t="n">
         <v>46217</v>
       </c>
       <c r="B104" s="28" t="inlineStr">
@@ -8880,7 +8968,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="20" t="n">
+      <c r="A105" s="31" t="n">
         <v>46217</v>
       </c>
       <c r="B105" s="14" t="inlineStr">
@@ -8904,7 +8992,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="20" t="n">
+      <c r="A106" s="31" t="n">
         <v>46216</v>
       </c>
       <c r="B106" s="14" t="inlineStr">
@@ -8928,7 +9016,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="20" t="n">
+      <c r="A107" s="31" t="n">
         <v>46216</v>
       </c>
       <c r="B107" s="14" t="inlineStr">
@@ -8952,7 +9040,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="20" t="n">
+      <c r="A108" s="31" t="n">
         <v>46216</v>
       </c>
       <c r="B108" s="14" t="inlineStr">
@@ -8976,7 +9064,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="20" t="n">
+      <c r="A109" s="31" t="n">
         <v>46216</v>
       </c>
       <c r="B109" s="14" t="inlineStr">
@@ -9000,7 +9088,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="20" t="n">
+      <c r="A110" s="31" t="n">
         <v>46216</v>
       </c>
       <c r="B110" s="14" t="inlineStr">
@@ -9024,7 +9112,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="20" t="n">
+      <c r="A111" s="31" t="n">
         <v>46216</v>
       </c>
       <c r="B111" s="14" t="inlineStr">
@@ -9048,7 +9136,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="20" t="n">
+      <c r="A112" s="31" t="n">
         <v>46216</v>
       </c>
       <c r="B112" s="14" t="inlineStr">
@@ -9072,7 +9160,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="20" t="n">
+      <c r="A113" s="31" t="n">
         <v>46216</v>
       </c>
       <c r="B113" s="14" t="inlineStr">
@@ -9096,7 +9184,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="20" t="n">
+      <c r="A114" s="31" t="n">
         <v>46216</v>
       </c>
       <c r="B114" s="14" t="inlineStr">
@@ -9120,7 +9208,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="27" t="n">
+      <c r="A115" s="34" t="n">
         <v>46216</v>
       </c>
       <c r="B115" s="28" t="inlineStr">
@@ -9144,7 +9232,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="20" t="n">
+      <c r="A116" s="31" t="n">
         <v>46215</v>
       </c>
       <c r="B116" s="14" t="inlineStr">
@@ -9168,7 +9256,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="20" t="n">
+      <c r="A117" s="31" t="n">
         <v>46215</v>
       </c>
       <c r="B117" s="14" t="inlineStr">
@@ -9192,7 +9280,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="20" t="n">
+      <c r="A118" s="31" t="n">
         <v>46214</v>
       </c>
       <c r="B118" s="14" t="inlineStr">
@@ -9216,7 +9304,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="20" t="n">
+      <c r="A119" s="31" t="n">
         <v>46214</v>
       </c>
       <c r="B119" s="14" t="inlineStr">
@@ -9240,7 +9328,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="20" t="n">
+      <c r="A120" s="31" t="n">
         <v>46213</v>
       </c>
       <c r="B120" s="14" t="inlineStr">
@@ -9264,7 +9352,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="27" t="n">
+      <c r="A121" s="34" t="n">
         <v>46212</v>
       </c>
       <c r="B121" s="28" t="inlineStr">
@@ -9288,7 +9376,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="27" t="n">
+      <c r="A122" s="34" t="n">
         <v>46212</v>
       </c>
       <c r="B122" s="28" t="inlineStr">
@@ -9312,7 +9400,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="20" t="n">
+      <c r="A123" s="31" t="n">
         <v>46212</v>
       </c>
       <c r="B123" s="14" t="inlineStr">
@@ -9336,7 +9424,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="27" t="n">
+      <c r="A124" s="34" t="n">
         <v>46212</v>
       </c>
       <c r="B124" s="28" t="inlineStr">
@@ -9360,7 +9448,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="20" t="n">
+      <c r="A125" s="31" t="n">
         <v>46211</v>
       </c>
       <c r="B125" s="14" t="inlineStr">
@@ -9384,7 +9472,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="20" t="n">
+      <c r="A126" s="31" t="n">
         <v>46211</v>
       </c>
       <c r="B126" s="14" t="inlineStr">
@@ -9408,7 +9496,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="20" t="n">
+      <c r="A127" s="31" t="n">
         <v>46211</v>
       </c>
       <c r="B127" s="14" t="inlineStr">
@@ -9432,7 +9520,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="20" t="n">
+      <c r="A128" s="31" t="n">
         <v>46211</v>
       </c>
       <c r="B128" s="14" t="inlineStr">
@@ -9456,7 +9544,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="20" t="n">
+      <c r="A129" s="31" t="n">
         <v>46211</v>
       </c>
       <c r="B129" s="14" t="inlineStr">
@@ -9480,7 +9568,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="20" t="n">
+      <c r="A130" s="31" t="n">
         <v>46211</v>
       </c>
       <c r="B130" s="14" t="inlineStr">
@@ -9504,7 +9592,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="20" t="n">
+      <c r="A131" s="31" t="n">
         <v>46211</v>
       </c>
       <c r="B131" s="14" t="inlineStr">
@@ -9528,7 +9616,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="20" t="n">
+      <c r="A132" s="31" t="n">
         <v>46211</v>
       </c>
       <c r="B132" s="14" t="inlineStr">
@@ -9552,7 +9640,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="20" t="n">
+      <c r="A133" s="31" t="n">
         <v>46211</v>
       </c>
       <c r="B133" s="14" t="inlineStr">
@@ -9576,7 +9664,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="20" t="n">
+      <c r="A134" s="31" t="n">
         <v>46210</v>
       </c>
       <c r="B134" s="14" t="inlineStr">
@@ -9600,7 +9688,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="27" t="n">
+      <c r="A135" s="34" t="n">
         <v>46210</v>
       </c>
       <c r="B135" s="28" t="inlineStr">
@@ -9624,7 +9712,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="20" t="n">
+      <c r="A136" s="31" t="n">
         <v>46210</v>
       </c>
       <c r="B136" s="14" t="inlineStr">
@@ -9648,7 +9736,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="20" t="n">
+      <c r="A137" s="31" t="n">
         <v>46210</v>
       </c>
       <c r="B137" s="14" t="inlineStr">
@@ -9672,7 +9760,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="20" t="n">
+      <c r="A138" s="31" t="n">
         <v>46210</v>
       </c>
       <c r="B138" s="14" t="inlineStr">
@@ -9696,7 +9784,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="27" t="n">
+      <c r="A139" s="34" t="n">
         <v>46210</v>
       </c>
       <c r="B139" s="28" t="inlineStr">
@@ -9720,7 +9808,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="20" t="n">
+      <c r="A140" s="31" t="n">
         <v>46210</v>
       </c>
       <c r="B140" s="14" t="inlineStr">
@@ -9744,7 +9832,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="20" t="n">
+      <c r="A141" s="31" t="n">
         <v>46210</v>
       </c>
       <c r="B141" s="14" t="inlineStr">
@@ -9768,7 +9856,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="27" t="n">
+      <c r="A142" s="34" t="n">
         <v>46209</v>
       </c>
       <c r="B142" s="28" t="inlineStr">
@@ -9792,7 +9880,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="20" t="n">
+      <c r="A143" s="31" t="n">
         <v>46209</v>
       </c>
       <c r="B143" s="14" t="inlineStr">
@@ -9816,7 +9904,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="27" t="n">
+      <c r="A144" s="34" t="n">
         <v>46209</v>
       </c>
       <c r="B144" s="28" t="inlineStr">
@@ -9840,7 +9928,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="20" t="n">
+      <c r="A145" s="31" t="n">
         <v>46209</v>
       </c>
       <c r="B145" s="14" t="inlineStr">
@@ -9864,7 +9952,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="20" t="n">
+      <c r="A146" s="31" t="n">
         <v>46209</v>
       </c>
       <c r="B146" s="14" t="inlineStr">
@@ -9888,7 +9976,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="27" t="n">
+      <c r="A147" s="34" t="n">
         <v>46209</v>
       </c>
       <c r="B147" s="28" t="inlineStr">
@@ -9912,7 +10000,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="27" t="n">
+      <c r="A148" s="34" t="n">
         <v>46209</v>
       </c>
       <c r="B148" s="28" t="inlineStr">
@@ -9936,7 +10024,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="20" t="n">
+      <c r="A149" s="31" t="n">
         <v>46209</v>
       </c>
       <c r="B149" s="14" t="inlineStr">
@@ -9960,7 +10048,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="27" t="n">
+      <c r="A150" s="34" t="n">
         <v>46209</v>
       </c>
       <c r="B150" s="28" t="inlineStr">
@@ -9984,7 +10072,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="20" t="n">
+      <c r="A151" s="31" t="n">
         <v>46208</v>
       </c>
       <c r="B151" s="14" t="inlineStr">
@@ -10008,7 +10096,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="20" t="n">
+      <c r="A152" s="31" t="n">
         <v>46208</v>
       </c>
       <c r="B152" s="14" t="inlineStr">
@@ -10032,7 +10120,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="20" t="n">
+      <c r="A153" s="31" t="n">
         <v>46208</v>
       </c>
       <c r="B153" s="14" t="inlineStr">
@@ -10056,7 +10144,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="20" t="n">
+      <c r="A154" s="31" t="n">
         <v>46208</v>
       </c>
       <c r="B154" s="14" t="inlineStr">
@@ -10080,7 +10168,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="20" t="n">
+      <c r="A155" s="31" t="n">
         <v>46208</v>
       </c>
       <c r="B155" s="14" t="inlineStr">
@@ -10104,7 +10192,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="27" t="n">
+      <c r="A156" s="34" t="n">
         <v>46208</v>
       </c>
       <c r="B156" s="28" t="inlineStr">
@@ -10128,7 +10216,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="20" t="n">
+      <c r="A157" s="31" t="n">
         <v>46208</v>
       </c>
       <c r="B157" s="14" t="inlineStr">
@@ -10152,7 +10240,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="20" t="n">
+      <c r="A158" s="31" t="n">
         <v>46207</v>
       </c>
       <c r="B158" s="14" t="inlineStr">
@@ -10176,7 +10264,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="20" t="n">
+      <c r="A159" s="31" t="n">
         <v>46207</v>
       </c>
       <c r="B159" s="14" t="inlineStr">
@@ -10200,7 +10288,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="20" t="n">
+      <c r="A160" s="31" t="n">
         <v>46207</v>
       </c>
       <c r="B160" s="14" t="inlineStr">
@@ -10224,7 +10312,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="27" t="n">
+      <c r="A161" s="34" t="n">
         <v>46207</v>
       </c>
       <c r="B161" s="28" t="inlineStr">
@@ -10248,7 +10336,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="20" t="n">
+      <c r="A162" s="31" t="n">
         <v>46206</v>
       </c>
       <c r="B162" s="14" t="inlineStr">
@@ -10272,7 +10360,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="20" t="n">
+      <c r="A163" s="31" t="n">
         <v>46206</v>
       </c>
       <c r="B163" s="14" t="inlineStr">
@@ -10296,7 +10384,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="20" t="n">
+      <c r="A164" s="31" t="n">
         <v>46206</v>
       </c>
       <c r="B164" s="14" t="inlineStr">
@@ -10320,7 +10408,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="20" t="n">
+      <c r="A165" s="31" t="n">
         <v>46206</v>
       </c>
       <c r="B165" s="14" t="inlineStr">
@@ -10344,7 +10432,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="20" t="n">
+      <c r="A166" s="31" t="n">
         <v>46206</v>
       </c>
       <c r="B166" s="14" t="inlineStr">
@@ -10368,7 +10456,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="20" t="n">
+      <c r="A167" s="31" t="n">
         <v>46206</v>
       </c>
       <c r="B167" s="14" t="inlineStr">
@@ -10392,7 +10480,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="20" t="n">
+      <c r="A168" s="31" t="n">
         <v>46206</v>
       </c>
       <c r="B168" s="14" t="inlineStr">
@@ -10416,7 +10504,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="20" t="n">
+      <c r="A169" s="31" t="n">
         <v>46205</v>
       </c>
       <c r="B169" s="14" t="inlineStr">
@@ -10440,7 +10528,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="27" t="n">
+      <c r="A170" s="34" t="n">
         <v>46205</v>
       </c>
       <c r="B170" s="28" t="inlineStr">
@@ -10464,7 +10552,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="20" t="n">
+      <c r="A171" s="31" t="n">
         <v>46205</v>
       </c>
       <c r="B171" s="14" t="inlineStr">
@@ -10488,7 +10576,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="20" t="n">
+      <c r="A172" s="31" t="n">
         <v>46205</v>
       </c>
       <c r="B172" s="14" t="inlineStr">
@@ -10512,7 +10600,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="27" t="n">
+      <c r="A173" s="34" t="n">
         <v>46205</v>
       </c>
       <c r="B173" s="28" t="inlineStr">
@@ -10536,7 +10624,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="20" t="n">
+      <c r="A174" s="31" t="n">
         <v>46205</v>
       </c>
       <c r="B174" s="14" t="inlineStr">
@@ -10560,7 +10648,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="20" t="n">
+      <c r="A175" s="31" t="n">
         <v>46204</v>
       </c>
       <c r="B175" s="14" t="inlineStr">
@@ -10584,7 +10672,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="27" t="n">
+      <c r="A176" s="34" t="n">
         <v>46204</v>
       </c>
       <c r="B176" s="28" t="inlineStr">
@@ -10612,7 +10700,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="27" t="n">
+      <c r="A177" s="34" t="n">
         <v>46204</v>
       </c>
       <c r="B177" s="28" t="inlineStr">
@@ -10640,7 +10728,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="27" t="n">
+      <c r="A178" s="34" t="n">
         <v>46204</v>
       </c>
       <c r="B178" s="28" t="inlineStr">
@@ -10664,7 +10752,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="20" t="n">
+      <c r="A179" s="31" t="n">
         <v>46204</v>
       </c>
       <c r="B179" s="14" t="inlineStr">
@@ -10688,7 +10776,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="27" t="n">
+      <c r="A180" s="34" t="n">
         <v>46204</v>
       </c>
       <c r="B180" s="28" t="inlineStr">
@@ -10712,7 +10800,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="20" t="n">
+      <c r="A181" s="31" t="n">
         <v>46204</v>
       </c>
       <c r="B181" s="14" t="inlineStr">
@@ -10736,7 +10824,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="20" t="n">
+      <c r="A182" s="31" t="n">
         <v>46204</v>
       </c>
       <c r="B182" s="14" t="inlineStr">
@@ -10760,7 +10848,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="20" t="n">
+      <c r="A183" s="31" t="n">
         <v>46204</v>
       </c>
       <c r="B183" s="14" t="inlineStr">
@@ -10784,7 +10872,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="20" t="n">
+      <c r="A184" s="31" t="n">
         <v>46204</v>
       </c>
       <c r="B184" s="14" t="inlineStr">
@@ -10808,7 +10896,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="20" t="n">
+      <c r="A185" s="31" t="n">
         <v>46204</v>
       </c>
       <c r="B185" s="14" t="inlineStr">
@@ -10832,7 +10920,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="20" t="n">
+      <c r="A186" s="31" t="n">
         <v>46204</v>
       </c>
       <c r="B186" s="14" t="inlineStr">
@@ -10856,7 +10944,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="20" t="n">
+      <c r="A187" s="31" t="n">
         <v>46204</v>
       </c>
       <c r="B187" s="14" t="inlineStr">
@@ -10880,7 +10968,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="20" t="n">
+      <c r="A188" s="31" t="n">
         <v>46204</v>
       </c>
       <c r="B188" s="14" t="inlineStr">
@@ -10904,7 +10992,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="20" t="n">
+      <c r="A189" s="31" t="n">
         <v>46203</v>
       </c>
       <c r="B189" s="14" t="inlineStr">
@@ -10928,7 +11016,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="20" t="n">
+      <c r="A190" s="31" t="n">
         <v>46203</v>
       </c>
       <c r="B190" s="14" t="inlineStr">
@@ -10952,7 +11040,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="20" t="n">
+      <c r="A191" s="31" t="n">
         <v>46180</v>
       </c>
       <c r="B191" s="14" t="inlineStr">
@@ -10980,7 +11068,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="20" t="n">
+      <c r="A192" s="31" t="n">
         <v>46177</v>
       </c>
       <c r="B192" s="14" t="inlineStr">
@@ -11008,7 +11096,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="20" t="n">
+      <c r="A193" s="31" t="n">
         <v>46175</v>
       </c>
       <c r="B193" s="14" t="inlineStr">
@@ -11036,7 +11124,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="20" t="n">
+      <c r="A194" s="31" t="n">
         <v>45974</v>
       </c>
       <c r="B194" s="14" t="inlineStr">
@@ -11060,6 +11148,2071 @@
       <c r="F194" s="14" t="inlineStr">
         <is>
           <t>****9061</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F86"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Transacoes da Fatura Agosto sem correspondente no Excel controle Julho (cruzamento por valor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Lancamento</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Parcelamento</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>Valor R$</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Cartao</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>Classificacao</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="32" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Schipper Cons     </t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>Parcela 1 de 3</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="n">
+        <v>921.15</v>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>Mercadoria - DEVE LANCAR NO EXCEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="32" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tramontina        </t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>Parcela 9 de 10</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="n">
+        <v>402.35</v>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>Mercadoria - DEVE LANCAR NO EXCEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="32" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>Imigbeb*imigbebidas</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="n"/>
+      <c r="D6" s="23" t="n">
+        <v>337.86</v>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>Mercadoria - DEVE LANCAR NO EXCEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="32" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>Netfeira</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="23" t="n">
+        <v>315.17</v>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>****4280</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>Mercadoria - DEVE LANCAR NO EXCEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="32" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>Sonda S*sonda1451154</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="n"/>
+      <c r="D8" s="23" t="n">
+        <v>313.9</v>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>Mercadoria - DEVE LANCAR NO EXCEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="32" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>Kalunga.com</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="n"/>
+      <c r="D9" s="23" t="n">
+        <v>298.22</v>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>Mercadoria - DEVE LANCAR NO EXCEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="32" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>Mp *Tiagohenriquealves</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="23" t="n">
+        <v>19</v>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>****4280</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>Mercadoria - DEVE LANCAR NO EXCEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="32" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>Mp *Madalenaaguas</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>****4280</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>Mercadoria - DEVE LANCAR NO EXCEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="34" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>Google Ads2978776244</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="n"/>
+      <c r="D12" s="29" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E12" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="34" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>Google Ads2978776244</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="n"/>
+      <c r="D13" s="29" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F13" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Google Ads2978776244</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="n"/>
+      <c r="D14" s="29" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F14" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>Google Ads2978776244</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="n"/>
+      <c r="D15" s="29" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E15" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F15" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>Google Ads2978776244</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="29" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E16" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F16" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="34" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B17" s="28" t="inlineStr">
+        <is>
+          <t>Google Ads2978776244</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="n"/>
+      <c r="D17" s="29" t="n">
+        <v>1665.22</v>
+      </c>
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F17" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>Google Cloud Z7n7nc</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="n"/>
+      <c r="D18" s="29" t="n">
+        <v>1032.76</v>
+      </c>
+      <c r="E18" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F18" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="34" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>Mag*magalu-magazin</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>Parcela 2 de 10</t>
+        </is>
+      </c>
+      <c r="D19" s="29" t="n">
+        <v>629.9</v>
+      </c>
+      <c r="E19" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F19" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="34" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B20" s="28" t="inlineStr">
+        <is>
+          <t>Anthropic* Claude Sub</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="n"/>
+      <c r="D20" s="29" t="n">
+        <v>582.98</v>
+      </c>
+      <c r="E20" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F20" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="34" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B21" s="28" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="n"/>
+      <c r="D21" s="29" t="n">
+        <v>542</v>
+      </c>
+      <c r="E21" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F21" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="34" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B22" s="28" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="n"/>
+      <c r="D22" s="29" t="n">
+        <v>542</v>
+      </c>
+      <c r="E22" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F22" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="34" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B23" s="28" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="n"/>
+      <c r="D23" s="29" t="n">
+        <v>542</v>
+      </c>
+      <c r="E23" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F23" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="34" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B24" s="28" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="n"/>
+      <c r="D24" s="29" t="n">
+        <v>542</v>
+      </c>
+      <c r="E24" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F24" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="34" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B25" s="28" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="n"/>
+      <c r="D25" s="29" t="n">
+        <v>542</v>
+      </c>
+      <c r="E25" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F25" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="34" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B26" s="28" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="n"/>
+      <c r="D26" s="29" t="n">
+        <v>460.7</v>
+      </c>
+      <c r="E26" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F26" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="34" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B27" s="28" t="inlineStr">
+        <is>
+          <t>Mercadolivre*wwwcasace</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="n"/>
+      <c r="D27" s="29" t="n">
+        <v>419.94</v>
+      </c>
+      <c r="E27" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F27" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="34" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B28" s="28" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="n"/>
+      <c r="D28" s="29" t="n">
+        <v>245.22</v>
+      </c>
+      <c r="E28" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F28" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="34" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B29" s="28" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C29" s="28" t="n"/>
+      <c r="D29" s="29" t="n">
+        <v>136.75</v>
+      </c>
+      <c r="E29" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F29" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="34" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B30" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *D94j7wzt32</t>
+        </is>
+      </c>
+      <c r="C30" s="28" t="n"/>
+      <c r="D30" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E30" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F30" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="34" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B31" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *B89fsw5u32</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="n"/>
+      <c r="D31" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E31" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F31" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="34" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B32" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *Zb48eyru32</t>
+        </is>
+      </c>
+      <c r="C32" s="28" t="n"/>
+      <c r="D32" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E32" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F32" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="34" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B33" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *Szgeayru32</t>
+        </is>
+      </c>
+      <c r="C33" s="28" t="n"/>
+      <c r="D33" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E33" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F33" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="34" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B34" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *Fz7pqvzt32</t>
+        </is>
+      </c>
+      <c r="C34" s="28" t="n"/>
+      <c r="D34" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E34" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F34" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="34" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B35" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *2fl9eydu32</t>
+        </is>
+      </c>
+      <c r="C35" s="28" t="n"/>
+      <c r="D35" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E35" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F35" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="34" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B36" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *Xvndjvzt32</t>
+        </is>
+      </c>
+      <c r="C36" s="28" t="n"/>
+      <c r="D36" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E36" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F36" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="34" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B37" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *Bqlkwwhu32</t>
+        </is>
+      </c>
+      <c r="C37" s="28" t="n"/>
+      <c r="D37" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E37" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F37" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="34" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B38" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *X7gzavzt32</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="n"/>
+      <c r="D38" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E38" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F38" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="34" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B39" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *3mv5jvvt32</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="n"/>
+      <c r="D39" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E39" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F39" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="34" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B40" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *Wban3wvu32</t>
+        </is>
+      </c>
+      <c r="C40" s="28" t="n"/>
+      <c r="D40" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E40" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F40" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="34" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B41" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *Rr5fdxru32</t>
+        </is>
+      </c>
+      <c r="C41" s="28" t="n"/>
+      <c r="D41" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E41" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F41" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="34" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B42" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *Wthunu9u32</t>
+        </is>
+      </c>
+      <c r="C42" s="28" t="n"/>
+      <c r="D42" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E42" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F42" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="34" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B43" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *V3s6ku9u32</t>
+        </is>
+      </c>
+      <c r="C43" s="28" t="n"/>
+      <c r="D43" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E43" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F43" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="34" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B44" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *X6atmuzt32</t>
+        </is>
+      </c>
+      <c r="C44" s="28" t="n"/>
+      <c r="D44" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E44" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F44" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="34" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B45" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *89bvxwru32</t>
+        </is>
+      </c>
+      <c r="C45" s="28" t="n"/>
+      <c r="D45" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E45" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F45" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="34" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B46" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *95zw8u9u32</t>
+        </is>
+      </c>
+      <c r="C46" s="28" t="n"/>
+      <c r="D46" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E46" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F46" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="34" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B47" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *Qcvwwu5u32</t>
+        </is>
+      </c>
+      <c r="C47" s="28" t="n"/>
+      <c r="D47" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E47" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F47" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="34" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B48" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *52mc5vvu32</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="n"/>
+      <c r="D48" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E48" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F48" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="34" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B49" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *Pnfpqu5u32</t>
+        </is>
+      </c>
+      <c r="C49" s="28" t="n"/>
+      <c r="D49" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E49" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F49" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="34" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B50" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *7xagmu5u32</t>
+        </is>
+      </c>
+      <c r="C50" s="28" t="n"/>
+      <c r="D50" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E50" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F50" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="34" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B51" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *8gdtkwdu32</t>
+        </is>
+      </c>
+      <c r="C51" s="28" t="n"/>
+      <c r="D51" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E51" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F51" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="34" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B52" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *Lcxkqtzt32</t>
+        </is>
+      </c>
+      <c r="C52" s="28" t="n"/>
+      <c r="D52" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E52" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F52" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="34" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B53" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *Sveadwdu32</t>
+        </is>
+      </c>
+      <c r="C53" s="28" t="n"/>
+      <c r="D53" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E53" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F53" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="34" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B54" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *Q32vhtzt32</t>
+        </is>
+      </c>
+      <c r="C54" s="28" t="n"/>
+      <c r="D54" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E54" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F54" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="34" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B55" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *Lxn35u5u32</t>
+        </is>
+      </c>
+      <c r="C55" s="28" t="n"/>
+      <c r="D55" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E55" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F55" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="34" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B56" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *26gtmtvt32</t>
+        </is>
+      </c>
+      <c r="C56" s="28" t="n"/>
+      <c r="D56" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E56" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F56" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="34" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B57" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *F5rfxvdu32</t>
+        </is>
+      </c>
+      <c r="C57" s="28" t="n"/>
+      <c r="D57" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E57" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F57" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="34" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B58" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *6hnqdsmu32</t>
+        </is>
+      </c>
+      <c r="C58" s="28" t="n"/>
+      <c r="D58" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E58" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F58" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="34" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B59" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *Dtc4asmu32</t>
+        </is>
+      </c>
+      <c r="C59" s="28" t="n"/>
+      <c r="D59" s="29" t="n">
+        <v>130</v>
+      </c>
+      <c r="E59" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F59" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="34" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B60" s="28" t="inlineStr">
+        <is>
+          <t>Lalamove Tecnologia Br</t>
+        </is>
+      </c>
+      <c r="C60" s="28" t="n"/>
+      <c r="D60" s="29" t="n">
+        <v>125</v>
+      </c>
+      <c r="E60" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F60" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="34" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B61" s="28" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C61" s="28" t="n"/>
+      <c r="D61" s="29" t="n">
+        <v>110</v>
+      </c>
+      <c r="E61" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F61" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="34" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B62" s="28" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C62" s="28" t="n"/>
+      <c r="D62" s="29" t="n">
+        <v>110</v>
+      </c>
+      <c r="E62" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F62" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="34" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B63" s="28" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C63" s="28" t="n"/>
+      <c r="D63" s="29" t="n">
+        <v>110</v>
+      </c>
+      <c r="E63" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F63" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="34" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B64" s="28" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C64" s="28" t="n"/>
+      <c r="D64" s="29" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="E64" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F64" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="34" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B65" s="28" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C65" s="28" t="n"/>
+      <c r="D65" s="29" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="E65" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F65" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="34" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B66" s="28" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C66" s="28" t="n"/>
+      <c r="D66" s="29" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="E66" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F66" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="34" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B67" s="28" t="inlineStr">
+        <is>
+          <t>Google Workspace_pedem</t>
+        </is>
+      </c>
+      <c r="C67" s="28" t="n"/>
+      <c r="D67" s="29" t="n">
+        <v>94.73</v>
+      </c>
+      <c r="E67" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F67" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="34" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B68" s="28" t="inlineStr">
+        <is>
+          <t>99*</t>
+        </is>
+      </c>
+      <c r="C68" s="28" t="n"/>
+      <c r="D68" s="29" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="E68" s="28" t="inlineStr">
+        <is>
+          <t>****4280</t>
+        </is>
+      </c>
+      <c r="F68" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="34" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B69" s="28" t="inlineStr">
+        <is>
+          <t>Facebk *W577asmu32</t>
+        </is>
+      </c>
+      <c r="C69" s="28" t="n"/>
+      <c r="D69" s="29" t="n">
+        <v>88.55</v>
+      </c>
+      <c r="E69" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F69" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="34" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B70" s="28" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C70" s="28" t="n"/>
+      <c r="D70" s="29" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="E70" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F70" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="34" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B71" s="28" t="inlineStr">
+        <is>
+          <t>Ryze Ai</t>
+        </is>
+      </c>
+      <c r="C71" s="28" t="n"/>
+      <c r="D71" s="29" t="n">
+        <v>56.93</v>
+      </c>
+      <c r="E71" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F71" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="34" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B72" s="28" t="inlineStr">
+        <is>
+          <t>Ryze Ai</t>
+        </is>
+      </c>
+      <c r="C72" s="28" t="n"/>
+      <c r="D72" s="29" t="n">
+        <v>56.37</v>
+      </c>
+      <c r="E72" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F72" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="34" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B73" s="28" t="inlineStr">
+        <is>
+          <t>Ryze Ai</t>
+        </is>
+      </c>
+      <c r="C73" s="28" t="n"/>
+      <c r="D73" s="29" t="n">
+        <v>56.21</v>
+      </c>
+      <c r="E73" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F73" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="34" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B74" s="28" t="inlineStr">
+        <is>
+          <t>Ryze Ai</t>
+        </is>
+      </c>
+      <c r="C74" s="28" t="n"/>
+      <c r="D74" s="29" t="n">
+        <v>56.01</v>
+      </c>
+      <c r="E74" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F74" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="34" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B75" s="28" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C75" s="28" t="n"/>
+      <c r="D75" s="29" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="E75" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F75" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="34" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B76" s="28" t="inlineStr">
+        <is>
+          <t>Tim*11981472453</t>
+        </is>
+      </c>
+      <c r="C76" s="28" t="n"/>
+      <c r="D76" s="29" t="n">
+        <v>49.99</v>
+      </c>
+      <c r="E76" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F76" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="34" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B77" s="28" t="inlineStr">
+        <is>
+          <t>Setti Soluco*comemorea</t>
+        </is>
+      </c>
+      <c r="C77" s="28" t="n"/>
+      <c r="D77" s="29" t="n">
+        <v>49</v>
+      </c>
+      <c r="E77" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F77" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="34" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B78" s="28" t="inlineStr">
+        <is>
+          <t>Dm*spotify</t>
+        </is>
+      </c>
+      <c r="C78" s="28" t="n"/>
+      <c r="D78" s="29" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="E78" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F78" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="34" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B79" s="28" t="inlineStr">
+        <is>
+          <t>Ebn*canva0494</t>
+        </is>
+      </c>
+      <c r="C79" s="28" t="n"/>
+      <c r="D79" s="29" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="E79" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F79" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="34" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B80" s="28" t="inlineStr">
+        <is>
+          <t>Ryze Ai</t>
+        </is>
+      </c>
+      <c r="C80" s="28" t="n"/>
+      <c r="D80" s="29" t="n">
+        <v>27.77</v>
+      </c>
+      <c r="E80" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F80" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="34" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B81" s="28" t="inlineStr">
+        <is>
+          <t>Ryze Ai</t>
+        </is>
+      </c>
+      <c r="C81" s="28" t="n"/>
+      <c r="D81" s="29" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="E81" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F81" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="34" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B82" s="28" t="inlineStr">
+        <is>
+          <t>Uber Uber *Trip Help.u</t>
+        </is>
+      </c>
+      <c r="C82" s="28" t="n"/>
+      <c r="D82" s="29" t="n">
+        <v>22.93</v>
+      </c>
+      <c r="E82" s="28" t="inlineStr">
+        <is>
+          <t>****4280</t>
+        </is>
+      </c>
+      <c r="F82" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="34" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B83" s="28" t="inlineStr">
+        <is>
+          <t>Ryze Ai</t>
+        </is>
+      </c>
+      <c r="C83" s="28" t="n"/>
+      <c r="D83" s="29" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="E83" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F83" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="34" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B84" s="28" t="inlineStr">
+        <is>
+          <t>Ryze Ai</t>
+        </is>
+      </c>
+      <c r="C84" s="28" t="n"/>
+      <c r="D84" s="29" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="E84" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F84" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="34" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B85" s="28" t="inlineStr">
+        <is>
+          <t>Ryze Ai</t>
+        </is>
+      </c>
+      <c r="C85" s="28" t="n"/>
+      <c r="D85" s="29" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="E85" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F85" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="34" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B86" s="28" t="inlineStr">
+        <is>
+          <t>Mercado*mercadolivre</t>
+        </is>
+      </c>
+      <c r="C86" s="28" t="n"/>
+      <c r="D86" s="29" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="E86" s="28" t="inlineStr">
+        <is>
+          <t>****9061</t>
+        </is>
+      </c>
+      <c r="F86" s="28" t="inlineStr">
+        <is>
+          <t>Servico/app (sem DANFE)</t>
         </is>
       </c>
     </row>
